--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2810,6 +2810,121 @@
         <v>5118100</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C104" t="n">
+        <v>158.6000061035156</v>
+      </c>
+      <c r="D104" t="n">
+        <v>159.1699981689453</v>
+      </c>
+      <c r="E104" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>158.0399932861328</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3407100</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C105" t="n">
+        <v>159.3500061035156</v>
+      </c>
+      <c r="D105" t="n">
+        <v>159.4100036621094</v>
+      </c>
+      <c r="E105" t="n">
+        <v>158.4199981689453</v>
+      </c>
+      <c r="F105" t="n">
+        <v>158.6499938964844</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2967600</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C106" t="n">
+        <v>157.9499969482422</v>
+      </c>
+      <c r="D106" t="n">
+        <v>159</v>
+      </c>
+      <c r="E106" t="n">
+        <v>157.8099975585938</v>
+      </c>
+      <c r="F106" t="n">
+        <v>159</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3336600</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C107" t="n">
+        <v>158.5399932861328</v>
+      </c>
+      <c r="D107" t="n">
+        <v>158.75</v>
+      </c>
+      <c r="E107" t="n">
+        <v>157.4600067138672</v>
+      </c>
+      <c r="F107" t="n">
+        <v>157.5700073242188</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2216100</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C108" t="n">
+        <v>153.6799926757812</v>
+      </c>
+      <c r="D108" t="n">
+        <v>157.0928039550781</v>
+      </c>
+      <c r="E108" t="n">
+        <v>153.2700042724609</v>
+      </c>
+      <c r="F108" t="n">
+        <v>157.0899963378906</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3977994</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,16 +2913,62 @@
         <v>153.6799926757812</v>
       </c>
       <c r="D108" t="n">
-        <v>157.0928039550781</v>
+        <v>157.0899963378906</v>
       </c>
       <c r="E108" t="n">
-        <v>153.2700042724609</v>
+        <v>153.2299957275391</v>
       </c>
       <c r="F108" t="n">
         <v>157.0899963378906</v>
       </c>
       <c r="G108" t="n">
-        <v>3977994</v>
+        <v>3986400</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C109" t="n">
+        <v>154.4799957275391</v>
+      </c>
+      <c r="D109" t="n">
+        <v>155.6000061035156</v>
+      </c>
+      <c r="E109" t="n">
+        <v>154.2100067138672</v>
+      </c>
+      <c r="F109" t="n">
+        <v>155.1600036621094</v>
+      </c>
+      <c r="G109" t="n">
+        <v>5059000</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C110" t="n">
+        <v>154.3000030517578</v>
+      </c>
+      <c r="D110" t="n">
+        <v>156.5350036621094</v>
+      </c>
+      <c r="E110" t="n">
+        <v>151.1999969482422</v>
+      </c>
+      <c r="F110" t="n">
+        <v>155.7400054931641</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4997076</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -2956,7 +2956,7 @@
         <v>46182</v>
       </c>
       <c r="C110" t="n">
-        <v>154.3000030517578</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="D110" t="n">
         <v>156.5350036621094</v>
@@ -2968,7 +2968,7 @@
         <v>155.7400054931641</v>
       </c>
       <c r="G110" t="n">
-        <v>4997076</v>
+        <v>5033483</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -2956,7 +2956,7 @@
         <v>46182</v>
       </c>
       <c r="C110" t="n">
-        <v>154.2899932861328</v>
+        <v>154.3000030517578</v>
       </c>
       <c r="D110" t="n">
         <v>156.5350036621094</v>
@@ -2968,7 +2968,7 @@
         <v>155.7400054931641</v>
       </c>
       <c r="G110" t="n">
-        <v>5033483</v>
+        <v>5069604</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -2968,7 +2968,7 @@
         <v>155.7400054931641</v>
       </c>
       <c r="G110" t="n">
-        <v>5069604</v>
+        <v>5070870</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2959,7 +2959,7 @@
         <v>154.3000030517578</v>
       </c>
       <c r="D110" t="n">
-        <v>156.5350036621094</v>
+        <v>156.5599975585938</v>
       </c>
       <c r="E110" t="n">
         <v>151.1999969482422</v>
@@ -2968,7 +2968,76 @@
         <v>155.7400054931641</v>
       </c>
       <c r="G110" t="n">
-        <v>5070870</v>
+        <v>5115600</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C111" t="n">
+        <v>151.9199981689453</v>
+      </c>
+      <c r="D111" t="n">
+        <v>154.5700073242188</v>
+      </c>
+      <c r="E111" t="n">
+        <v>151.8800048828125</v>
+      </c>
+      <c r="F111" t="n">
+        <v>153.3699951171875</v>
+      </c>
+      <c r="G111" t="n">
+        <v>5763500</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C112" t="n">
+        <v>155.6100006103516</v>
+      </c>
+      <c r="D112" t="n">
+        <v>155.8800048828125</v>
+      </c>
+      <c r="E112" t="n">
+        <v>152.2400054931641</v>
+      </c>
+      <c r="F112" t="n">
+        <v>152.9199981689453</v>
+      </c>
+      <c r="G112" t="n">
+        <v>4852900</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C113" t="n">
+        <v>156.2899932861328</v>
+      </c>
+      <c r="D113" t="n">
+        <v>156.8399963378906</v>
+      </c>
+      <c r="E113" t="n">
+        <v>154.9199981689453</v>
+      </c>
+      <c r="F113" t="n">
+        <v>155.8999938964844</v>
+      </c>
+      <c r="G113" t="n">
+        <v>8976000</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>141.7670288085938</v>
+        <v>141.2567443847656</v>
       </c>
       <c r="D2" t="n">
-        <v>142.1361569309328</v>
+        <v>141.6245438460415</v>
       </c>
       <c r="E2" t="n">
-        <v>141.0487147381264</v>
+        <v>140.5410158554122</v>
       </c>
       <c r="F2" t="n">
-        <v>141.9266423174491</v>
+        <v>141.4157833715471</v>
       </c>
       <c r="G2" t="n">
         <v>4387700</v>
@@ -495,16 +495,16 @@
         <v>46027</v>
       </c>
       <c r="C3" t="n">
-        <v>142.9642181396484</v>
+        <v>142.4496154785156</v>
       </c>
       <c r="D3" t="n">
-        <v>143.1637464489775</v>
+        <v>142.648425581567</v>
       </c>
       <c r="E3" t="n">
-        <v>142.345660590784</v>
+        <v>141.8332844403463</v>
       </c>
       <c r="F3" t="n">
-        <v>142.3955464738748</v>
+        <v>141.8829907581688</v>
       </c>
       <c r="G3" t="n">
         <v>7382400</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>143.80224609375</v>
+        <v>143.2846374511719</v>
       </c>
       <c r="D4" t="n">
-        <v>143.8820604620446</v>
+        <v>143.364164531834</v>
       </c>
       <c r="E4" t="n">
-        <v>143.153775283028</v>
+        <v>142.6385007771216</v>
       </c>
       <c r="F4" t="n">
-        <v>143.2136322534904</v>
+        <v>142.6981422955583</v>
       </c>
       <c r="G4" t="n">
         <v>4700600</v>
@@ -541,16 +541,16 @@
         <v>46029</v>
       </c>
       <c r="C5" t="n">
-        <v>143.2036437988281</v>
+        <v>142.6881713867188</v>
       </c>
       <c r="D5" t="n">
-        <v>143.931944189974</v>
+        <v>143.4138502051908</v>
       </c>
       <c r="E5" t="n">
-        <v>143.1238446547625</v>
+        <v>142.6086594857441</v>
       </c>
       <c r="F5" t="n">
-        <v>143.7822865430245</v>
+        <v>143.264731262329</v>
       </c>
       <c r="G5" t="n">
         <v>7542300</v>
@@ -564,16 +564,16 @@
         <v>46030</v>
       </c>
       <c r="C6" t="n">
-        <v>143.3034210205078</v>
+        <v>142.78759765625</v>
       </c>
       <c r="D6" t="n">
-        <v>143.3832353906467</v>
+        <v>142.8671247330597</v>
       </c>
       <c r="E6" t="n">
-        <v>142.784635226122</v>
+        <v>142.2706792411067</v>
       </c>
       <c r="F6" t="n">
-        <v>142.9841787629866</v>
+        <v>142.4695045172503</v>
       </c>
       <c r="G6" t="n">
         <v>3070000</v>
@@ -587,16 +587,16 @@
         <v>46031</v>
       </c>
       <c r="C7" t="n">
-        <v>144.2511901855469</v>
+        <v>143.7319488525391</v>
       </c>
       <c r="D7" t="n">
-        <v>144.4207900114049</v>
+        <v>143.9009381930379</v>
       </c>
       <c r="E7" t="n">
-        <v>143.3832336582043</v>
+        <v>142.867116589916</v>
       </c>
       <c r="F7" t="n">
-        <v>143.5827619696235</v>
+        <v>143.0659266864889</v>
       </c>
       <c r="G7" t="n">
         <v>3998700</v>
@@ -610,16 +610,16 @@
         <v>46034</v>
       </c>
       <c r="C8" t="n">
-        <v>144.8996734619141</v>
+        <v>144.3780975341797</v>
       </c>
       <c r="D8" t="n">
-        <v>144.9794878295659</v>
+        <v>144.457624604753</v>
       </c>
       <c r="E8" t="n">
-        <v>144.0317017280971</v>
+        <v>143.5132501218432</v>
       </c>
       <c r="F8" t="n">
-        <v>144.0416880384499</v>
+        <v>143.5232004858135</v>
       </c>
       <c r="G8" t="n">
         <v>3400800</v>
@@ -633,16 +633,16 @@
         <v>46035</v>
       </c>
       <c r="C9" t="n">
-        <v>144.3609313964844</v>
+        <v>143.8412933349609</v>
       </c>
       <c r="D9" t="n">
-        <v>144.9196167513104</v>
+        <v>144.3979676597113</v>
       </c>
       <c r="E9" t="n">
-        <v>144.0416891464556</v>
+        <v>143.5232002214912</v>
       </c>
       <c r="F9" t="n">
-        <v>144.8398023830446</v>
+        <v>144.3184405892844</v>
       </c>
       <c r="G9" t="n">
         <v>4232100</v>
@@ -656,16 +656,16 @@
         <v>46036</v>
       </c>
       <c r="C10" t="n">
-        <v>144.2611694335938</v>
+        <v>143.7418975830078</v>
       </c>
       <c r="D10" t="n">
-        <v>144.3409685758273</v>
+        <v>143.8214094861428</v>
       </c>
       <c r="E10" t="n">
-        <v>143.5029405750726</v>
+        <v>142.9863979890842</v>
       </c>
       <c r="F10" t="n">
-        <v>144.1514265842306</v>
+        <v>143.6325497558998</v>
       </c>
       <c r="G10" t="n">
         <v>4545100</v>
@@ -679,16 +679,16 @@
         <v>46037</v>
       </c>
       <c r="C11" t="n">
-        <v>144.5903930664062</v>
+        <v>144.0699310302734</v>
       </c>
       <c r="D11" t="n">
-        <v>145.2089506355648</v>
+        <v>144.6862620633179</v>
       </c>
       <c r="E11" t="n">
-        <v>144.4906365199859</v>
+        <v>143.9705335636936</v>
       </c>
       <c r="F11" t="n">
-        <v>144.9994360089232</v>
+        <v>144.4775015974948</v>
       </c>
       <c r="G11" t="n">
         <v>4058600</v>
@@ -702,16 +702,16 @@
         <v>46038</v>
       </c>
       <c r="C12" t="n">
-        <v>144.5903930664062</v>
+        <v>144.0699310302734</v>
       </c>
       <c r="D12" t="n">
-        <v>144.8996794625029</v>
+        <v>144.3781041309149</v>
       </c>
       <c r="E12" t="n">
-        <v>144.1414505499281</v>
+        <v>143.6226045100678</v>
       </c>
       <c r="F12" t="n">
-        <v>144.8896931517366</v>
+        <v>144.36815376649</v>
       </c>
       <c r="G12" t="n">
         <v>3127300</v>
@@ -725,16 +725,16 @@
         <v>46042</v>
       </c>
       <c r="C13" t="n">
-        <v>142.1161956787109</v>
+        <v>141.6046447753906</v>
       </c>
       <c r="D13" t="n">
-        <v>143.4031813629854</v>
+        <v>142.8869979215774</v>
       </c>
       <c r="E13" t="n">
-        <v>141.9465958643169</v>
+        <v>141.4356554398927</v>
       </c>
       <c r="F13" t="n">
-        <v>142.8245386428586</v>
+        <v>142.3104380408116</v>
       </c>
       <c r="G13" t="n">
         <v>7591400</v>
@@ -748,16 +748,16 @@
         <v>46043</v>
       </c>
       <c r="C14" t="n">
-        <v>143.7822875976562</v>
+        <v>143.2647399902344</v>
       </c>
       <c r="D14" t="n">
-        <v>144.4108162287793</v>
+        <v>143.891006218285</v>
       </c>
       <c r="E14" t="n">
-        <v>142.3955453080767</v>
+        <v>141.882989310999</v>
       </c>
       <c r="F14" t="n">
-        <v>142.7646886614991</v>
+        <v>142.2508039245429</v>
       </c>
       <c r="G14" t="n">
         <v>6825900</v>
@@ -771,16 +771,16 @@
         <v>46044</v>
       </c>
       <c r="C15" t="n">
-        <v>144.5804138183594</v>
+        <v>144.0599975585938</v>
       </c>
       <c r="D15" t="n">
-        <v>144.9894567377894</v>
+        <v>144.467568130694</v>
       </c>
       <c r="E15" t="n">
-        <v>144.2212567808413</v>
+        <v>143.7021333044976</v>
       </c>
       <c r="F15" t="n">
-        <v>144.6602281848116</v>
+        <v>144.1395246337527</v>
       </c>
       <c r="G15" t="n">
         <v>5293000</v>
@@ -794,16 +794,16 @@
         <v>46045</v>
       </c>
       <c r="C16" t="n">
-        <v>144.8597564697266</v>
+        <v>144.3383331298828</v>
       </c>
       <c r="D16" t="n">
-        <v>144.9794856309055</v>
+        <v>144.4576313254119</v>
       </c>
       <c r="E16" t="n">
-        <v>144.1713708793243</v>
+        <v>143.6524253864851</v>
       </c>
       <c r="F16" t="n">
-        <v>144.4008428914809</v>
+        <v>143.88107141311</v>
       </c>
       <c r="G16" t="n">
         <v>3791700</v>
@@ -817,16 +817,16 @@
         <v>46048</v>
       </c>
       <c r="C17" t="n">
-        <v>145.4982604980469</v>
+        <v>144.9745330810547</v>
       </c>
       <c r="D17" t="n">
-        <v>145.8075316627933</v>
+        <v>145.2826910105795</v>
       </c>
       <c r="E17" t="n">
-        <v>145.1889893333005</v>
+        <v>144.6663751515298</v>
       </c>
       <c r="F17" t="n">
-        <v>145.3286606729612</v>
+        <v>144.8055437380326</v>
       </c>
       <c r="G17" t="n">
         <v>4678600</v>
@@ -840,16 +840,16 @@
         <v>46049</v>
       </c>
       <c r="C18" t="n">
-        <v>146.7054290771484</v>
+        <v>146.1773529052734</v>
       </c>
       <c r="D18" t="n">
-        <v>146.8051856189707</v>
+        <v>146.2767503666373</v>
       </c>
       <c r="E18" t="n">
-        <v>146.1367574189289</v>
+        <v>145.6107282193726</v>
       </c>
       <c r="F18" t="n">
-        <v>146.166685903779</v>
+        <v>145.6405489746055</v>
       </c>
       <c r="G18" t="n">
         <v>4936900</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>146.4560089111328</v>
+        <v>145.9288482666016</v>
       </c>
       <c r="D19" t="n">
-        <v>146.9149224754617</v>
+        <v>146.3861099958698</v>
       </c>
       <c r="E19" t="n">
-        <v>145.9771379500404</v>
+        <v>145.451700976162</v>
       </c>
       <c r="F19" t="n">
-        <v>146.805179627812</v>
+        <v>146.2767621617859</v>
       </c>
       <c r="G19" t="n">
         <v>4430300</v>
@@ -886,16 +886,16 @@
         <v>46051</v>
       </c>
       <c r="C20" t="n">
-        <v>146.3762054443359</v>
+        <v>145.8493194580078</v>
       </c>
       <c r="D20" t="n">
-        <v>147.1344191244316</v>
+        <v>146.604803922918</v>
       </c>
       <c r="E20" t="n">
-        <v>144.5105921184364</v>
+        <v>143.9904214688964</v>
       </c>
       <c r="F20" t="n">
-        <v>147.1344191244316</v>
+        <v>146.604803922918</v>
       </c>
       <c r="G20" t="n">
         <v>8850000</v>
@@ -909,16 +909,16 @@
         <v>46052</v>
       </c>
       <c r="C21" t="n">
-        <v>145.1091766357422</v>
+        <v>144.5868530273438</v>
       </c>
       <c r="D21" t="n">
-        <v>146.0569475388585</v>
+        <v>145.5312124086698</v>
       </c>
       <c r="E21" t="n">
-        <v>144.2611775005474</v>
+        <v>143.7419062833105</v>
       </c>
       <c r="F21" t="n">
-        <v>145.7576626811629</v>
+        <v>145.2330048332691</v>
       </c>
       <c r="G21" t="n">
         <v>13316000</v>
@@ -932,16 +932,16 @@
         <v>46055</v>
       </c>
       <c r="C22" t="n">
-        <v>145.8075256347656</v>
+        <v>145.2826843261719</v>
       </c>
       <c r="D22" t="n">
-        <v>146.0868683025385</v>
+        <v>145.5610214863712</v>
       </c>
       <c r="E22" t="n">
-        <v>144.7300697579467</v>
+        <v>144.2091068043958</v>
       </c>
       <c r="F22" t="n">
-        <v>144.8397973846119</v>
+        <v>144.3184394611106</v>
       </c>
       <c r="G22" t="n">
         <v>4177400</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>145.268798828125</v>
+        <v>144.7459106445312</v>
       </c>
       <c r="D23" t="n">
-        <v>146.2165696885264</v>
+        <v>145.6902700484627</v>
       </c>
       <c r="E23" t="n">
-        <v>144.0516563849033</v>
+        <v>143.5331492480756</v>
       </c>
       <c r="F23" t="n">
-        <v>146.1068268379726</v>
+        <v>145.5809222121186</v>
       </c>
       <c r="G23" t="n">
         <v>5718700</v>
@@ -978,16 +978,16 @@
         <v>46057</v>
       </c>
       <c r="C24" t="n">
-        <v>144.7899322509766</v>
+        <v>144.2687530517578</v>
       </c>
       <c r="D24" t="n">
-        <v>146.0569453913504</v>
+        <v>145.5312055097441</v>
       </c>
       <c r="E24" t="n">
-        <v>143.9718463905454</v>
+        <v>143.4536119356676</v>
       </c>
       <c r="F24" t="n">
-        <v>145.9272603626006</v>
+        <v>145.4019872892757</v>
       </c>
       <c r="G24" t="n">
         <v>7009800</v>
@@ -1001,16 +1001,16 @@
         <v>46058</v>
       </c>
       <c r="C25" t="n">
-        <v>143.0340423583984</v>
+        <v>142.5191802978516</v>
       </c>
       <c r="D25" t="n">
-        <v>144.370913963392</v>
+        <v>143.8512397304567</v>
       </c>
       <c r="E25" t="n">
-        <v>142.7846281726731</v>
+        <v>142.2706638977126</v>
       </c>
       <c r="F25" t="n">
-        <v>143.672542064934</v>
+        <v>143.1553816754778</v>
       </c>
       <c r="G25" t="n">
         <v>8561300</v>
@@ -1024,16 +1024,16 @@
         <v>46059</v>
       </c>
       <c r="C26" t="n">
-        <v>146.1168212890625</v>
+        <v>145.5908660888672</v>
       </c>
       <c r="D26" t="n">
-        <v>146.3163496039953</v>
+        <v>145.789676191113</v>
       </c>
       <c r="E26" t="n">
-        <v>144.2811212117909</v>
+        <v>143.7617737107853</v>
       </c>
       <c r="F26" t="n">
-        <v>144.3010786101945</v>
+        <v>143.7816592714814</v>
       </c>
       <c r="G26" t="n">
         <v>2636500</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>147.323974609375</v>
+        <v>146.7936706542969</v>
       </c>
       <c r="D27" t="n">
-        <v>147.5833598914135</v>
+        <v>147.0521222591024</v>
       </c>
       <c r="E27" t="n">
-        <v>145.9771470926316</v>
+        <v>145.4516911465814</v>
       </c>
       <c r="F27" t="n">
-        <v>146.1267895201472</v>
+        <v>145.6007949246927</v>
       </c>
       <c r="G27" t="n">
         <v>3890200</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>147.2341918945312</v>
+        <v>146.7042083740234</v>
       </c>
       <c r="D28" t="n">
-        <v>147.9525060060506</v>
+        <v>147.4199368453681</v>
       </c>
       <c r="E28" t="n">
-        <v>147.1942770977609</v>
+        <v>146.6644372543722</v>
       </c>
       <c r="F28" t="n">
-        <v>147.8726916355446</v>
+        <v>147.3404097743034</v>
       </c>
       <c r="G28" t="n">
         <v>3727000</v>
@@ -1093,16 +1093,16 @@
         <v>46064</v>
       </c>
       <c r="C29" t="n">
-        <v>147.6332397460938</v>
+        <v>147.1018371582031</v>
       </c>
       <c r="D29" t="n">
-        <v>148.3715112121023</v>
+        <v>147.837451232365</v>
       </c>
       <c r="E29" t="n">
-        <v>146.7752543429614</v>
+        <v>146.2469400545918</v>
       </c>
       <c r="F29" t="n">
-        <v>148.1819539963006</v>
+        <v>147.6485763235776</v>
       </c>
       <c r="G29" t="n">
         <v>4919800</v>
@@ -1116,16 +1116,16 @@
         <v>46065</v>
       </c>
       <c r="C30" t="n">
-        <v>145.6179809570312</v>
+        <v>145.0938262939453</v>
       </c>
       <c r="D30" t="n">
-        <v>148.3216221323354</v>
+        <v>147.7877356619546</v>
       </c>
       <c r="E30" t="n">
-        <v>145.4483659190517</v>
+        <v>144.9248217884873</v>
       </c>
       <c r="F30" t="n">
-        <v>148.1619934042567</v>
+        <v>147.6286815204869</v>
       </c>
       <c r="G30" t="n">
         <v>6120400</v>
@@ -1139,16 +1139,16 @@
         <v>46066</v>
       </c>
       <c r="C31" t="n">
-        <v>145.9970855712891</v>
+        <v>145.4715728759766</v>
       </c>
       <c r="D31" t="n">
-        <v>146.6555426817557</v>
+        <v>146.1276598872764</v>
       </c>
       <c r="E31" t="n">
-        <v>144.7500146301177</v>
+        <v>144.228990734078</v>
       </c>
       <c r="F31" t="n">
-        <v>145.538171989837</v>
+        <v>145.0143111419717</v>
       </c>
       <c r="G31" t="n">
         <v>5372200</v>
@@ -1162,16 +1162,16 @@
         <v>46070</v>
       </c>
       <c r="C32" t="n">
-        <v>145.9472045898438</v>
+        <v>145.4218597412109</v>
       </c>
       <c r="D32" t="n">
-        <v>146.3462764382395</v>
+        <v>145.8194951089261</v>
       </c>
       <c r="E32" t="n">
-        <v>144.4207909244367</v>
+        <v>143.9009404842666</v>
       </c>
       <c r="F32" t="n">
-        <v>145.288762680301</v>
+        <v>144.765787928898</v>
       </c>
       <c r="G32" t="n">
         <v>5586700</v>
@@ -1185,16 +1185,16 @@
         <v>46071</v>
       </c>
       <c r="C33" t="n">
-        <v>146.6655120849609</v>
+        <v>146.1375885009766</v>
       </c>
       <c r="D33" t="n">
-        <v>147.3139981007444</v>
+        <v>146.7837402866009</v>
       </c>
       <c r="E33" t="n">
-        <v>146.0070702050886</v>
+        <v>145.481516687469</v>
       </c>
       <c r="F33" t="n">
-        <v>146.2764265647044</v>
+        <v>145.7499034968973</v>
       </c>
       <c r="G33" t="n">
         <v>3300900</v>
@@ -1208,16 +1208,16 @@
         <v>46072</v>
       </c>
       <c r="C34" t="n">
-        <v>146.3362884521484</v>
+        <v>145.8095397949219</v>
       </c>
       <c r="D34" t="n">
-        <v>146.4161028209137</v>
+        <v>145.8890668657653</v>
       </c>
       <c r="E34" t="n">
-        <v>145.6778465501446</v>
+        <v>145.1534680048801</v>
       </c>
       <c r="F34" t="n">
-        <v>145.9771466272559</v>
+        <v>145.4516907284833</v>
       </c>
       <c r="G34" t="n">
         <v>3861100</v>
@@ -1231,16 +1231,16 @@
         <v>46073</v>
       </c>
       <c r="C35" t="n">
-        <v>147.6033172607422</v>
+        <v>147.072021484375</v>
       </c>
       <c r="D35" t="n">
-        <v>147.6931027172341</v>
+        <v>147.1614837595543</v>
       </c>
       <c r="E35" t="n">
-        <v>145.9172748702339</v>
+        <v>145.3920479764465</v>
       </c>
       <c r="F35" t="n">
-        <v>145.9871181517505</v>
+        <v>145.46163985819</v>
       </c>
       <c r="G35" t="n">
         <v>5087100</v>
@@ -1254,16 +1254,16 @@
         <v>46076</v>
       </c>
       <c r="C36" t="n">
-        <v>146.3063507080078</v>
+        <v>145.7797241210938</v>
       </c>
       <c r="D36" t="n">
-        <v>147.7529651186607</v>
+        <v>147.221131474049</v>
       </c>
       <c r="E36" t="n">
-        <v>145.8574082322684</v>
+        <v>145.3323976042145</v>
       </c>
       <c r="F36" t="n">
-        <v>147.3040074198879</v>
+        <v>146.7737897889314</v>
       </c>
       <c r="G36" t="n">
         <v>6073200</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>147.3538970947266</v>
+        <v>146.8235015869141</v>
       </c>
       <c r="D37" t="n">
-        <v>147.533483223467</v>
+        <v>147.0024413012886</v>
       </c>
       <c r="E37" t="n">
-        <v>145.9970833227078</v>
+        <v>145.4715716214576</v>
       </c>
       <c r="F37" t="n">
-        <v>146.256483817218</v>
+        <v>145.7300384124165</v>
       </c>
       <c r="G37" t="n">
         <v>6002800</v>
@@ -1300,16 +1300,16 @@
         <v>46078</v>
       </c>
       <c r="C38" t="n">
-        <v>148.5610656738281</v>
+        <v>148.0263214111328</v>
       </c>
       <c r="D38" t="n">
-        <v>148.660822211904</v>
+        <v>148.1257188764183</v>
       </c>
       <c r="E38" t="n">
-        <v>147.8726801020605</v>
+        <v>147.3404136772385</v>
       </c>
       <c r="F38" t="n">
-        <v>148.142051678629</v>
+        <v>147.608815653162</v>
       </c>
       <c r="G38" t="n">
         <v>5340100</v>
@@ -1323,16 +1323,16 @@
         <v>46079</v>
       </c>
       <c r="C39" t="n">
-        <v>148.0522613525391</v>
+        <v>147.5193481445312</v>
       </c>
       <c r="D39" t="n">
-        <v>148.7207047972324</v>
+        <v>148.1853855311392</v>
       </c>
       <c r="E39" t="n">
-        <v>146.9049621347581</v>
+        <v>146.3761786232582</v>
       </c>
       <c r="F39" t="n">
-        <v>148.7207047972324</v>
+        <v>148.1853855311392</v>
       </c>
       <c r="G39" t="n">
         <v>6394100</v>
@@ -1346,16 +1346,16 @@
         <v>46080</v>
       </c>
       <c r="C40" t="n">
-        <v>147.4935760498047</v>
+        <v>146.9626617431641</v>
       </c>
       <c r="D40" t="n">
-        <v>147.6831332754228</v>
+        <v>147.1515366431806</v>
       </c>
       <c r="E40" t="n">
-        <v>146.7652908561976</v>
+        <v>146.2369980673136</v>
       </c>
       <c r="F40" t="n">
-        <v>147.244161852525</v>
+        <v>146.7141453311924</v>
       </c>
       <c r="G40" t="n">
         <v>5198300</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>146.6056518554688</v>
+        <v>146.0779571533203</v>
       </c>
       <c r="D41" t="n">
-        <v>147.1144665250495</v>
+        <v>146.5849403873314</v>
       </c>
       <c r="E41" t="n">
-        <v>144.959524357849</v>
+        <v>144.4377547530523</v>
       </c>
       <c r="F41" t="n">
-        <v>145.1291241733648</v>
+        <v>144.6067441083095</v>
       </c>
       <c r="G41" t="n">
         <v>7713300</v>
@@ -1392,16 +1392,16 @@
         <v>46084</v>
       </c>
       <c r="C42" t="n">
-        <v>143.7024688720703</v>
+        <v>143.1852111816406</v>
       </c>
       <c r="D42" t="n">
-        <v>144.2711405159427</v>
+        <v>143.751835889344</v>
       </c>
       <c r="E42" t="n">
-        <v>140.9389706870736</v>
+        <v>140.4316602209324</v>
       </c>
       <c r="F42" t="n">
-        <v>142.5451986333182</v>
+        <v>142.0321065423775</v>
       </c>
       <c r="G42" t="n">
         <v>13870600</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>144.9196166992188</v>
+        <v>144.3979644775391</v>
       </c>
       <c r="D43" t="n">
-        <v>145.2488452595588</v>
+        <v>144.7260079477315</v>
       </c>
       <c r="E43" t="n">
-        <v>143.582760283075</v>
+        <v>143.0659202057788</v>
       </c>
       <c r="F43" t="n">
-        <v>144.1414456377002</v>
+        <v>143.6225945182615</v>
       </c>
       <c r="G43" t="n">
         <v>5318000</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>143.2335815429688</v>
+        <v>142.718017578125</v>
       </c>
       <c r="D44" t="n">
-        <v>144.5205520041593</v>
+        <v>144.0003556368688</v>
       </c>
       <c r="E44" t="n">
-        <v>141.9665532554473</v>
+        <v>141.4555499119358</v>
       </c>
       <c r="F44" t="n">
-        <v>143.672537709189</v>
+        <v>143.155393737904</v>
       </c>
       <c r="G44" t="n">
         <v>10527800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>141.597412109375</v>
+        <v>141.0877380371094</v>
       </c>
       <c r="D45" t="n">
-        <v>142.295783997458</v>
+        <v>141.7835961642497</v>
       </c>
       <c r="E45" t="n">
-        <v>140.6995271433162</v>
+        <v>140.1930849711274</v>
       </c>
       <c r="F45" t="n">
-        <v>141.3579842373772</v>
+        <v>140.8491719759083</v>
       </c>
       <c r="G45" t="n">
         <v>7498700</v>
@@ -1484,16 +1484,16 @@
         <v>46090</v>
       </c>
       <c r="C46" t="n">
-        <v>142.9043579101562</v>
+        <v>142.3899688720703</v>
       </c>
       <c r="D46" t="n">
-        <v>143.2834571223256</v>
+        <v>142.7677035038872</v>
       </c>
       <c r="E46" t="n">
-        <v>139.0234737735305</v>
+        <v>138.5230541082975</v>
       </c>
       <c r="F46" t="n">
-        <v>139.9812157256817</v>
+        <v>139.4773486361105</v>
       </c>
       <c r="G46" t="n">
         <v>9180700</v>
@@ -1507,16 +1507,16 @@
         <v>46091</v>
       </c>
       <c r="C47" t="n">
-        <v>142.8843994140625</v>
+        <v>142.3700866699219</v>
       </c>
       <c r="D47" t="n">
-        <v>144.6701982791956</v>
+        <v>144.1494575476849</v>
       </c>
       <c r="E47" t="n">
-        <v>142.4354569260041</v>
+        <v>141.9227601514441</v>
       </c>
       <c r="F47" t="n">
-        <v>143.0041133514024</v>
+        <v>142.4893696966524</v>
       </c>
       <c r="G47" t="n">
         <v>8055000</v>
@@ -1530,16 +1530,16 @@
         <v>46092</v>
       </c>
       <c r="C48" t="n">
-        <v>142.7048187255859</v>
+        <v>142.1911468505859</v>
       </c>
       <c r="D48" t="n">
-        <v>143.3932043376023</v>
+        <v>142.8770545902277</v>
       </c>
       <c r="E48" t="n">
-        <v>141.946605055137</v>
+        <v>141.4356624014852</v>
       </c>
       <c r="F48" t="n">
-        <v>142.7746620070528</v>
+        <v>142.2607387282833</v>
       </c>
       <c r="G48" t="n">
         <v>8392100</v>
@@ -1553,16 +1553,16 @@
         <v>46093</v>
       </c>
       <c r="C49" t="n">
-        <v>140.2206573486328</v>
+        <v>139.7159271240234</v>
       </c>
       <c r="D49" t="n">
-        <v>141.6273570005151</v>
+        <v>141.1175633006326</v>
       </c>
       <c r="E49" t="n">
-        <v>140.130871895883</v>
+        <v>139.6264648578325</v>
       </c>
       <c r="F49" t="n">
-        <v>141.4377997849096</v>
+        <v>140.9286884042933</v>
       </c>
       <c r="G49" t="n">
         <v>9415600</v>
@@ -1576,16 +1576,16 @@
         <v>46094</v>
       </c>
       <c r="C50" t="n">
-        <v>139.1930694580078</v>
+        <v>138.6920471191406</v>
       </c>
       <c r="D50" t="n">
-        <v>141.547539919721</v>
+        <v>141.0380427171116</v>
       </c>
       <c r="E50" t="n">
-        <v>139.0134833329192</v>
+        <v>138.5131074102908</v>
       </c>
       <c r="F50" t="n">
-        <v>140.9190113164609</v>
+        <v>140.4117764884947</v>
       </c>
       <c r="G50" t="n">
         <v>8763500</v>
@@ -1599,16 +1599,16 @@
         <v>46097</v>
       </c>
       <c r="C51" t="n">
-        <v>141.1584625244141</v>
+        <v>140.6503601074219</v>
       </c>
       <c r="D51" t="n">
-        <v>141.7371052804706</v>
+        <v>141.2269200285023</v>
       </c>
       <c r="E51" t="n">
-        <v>140.5698334578691</v>
+        <v>140.0638498217568</v>
       </c>
       <c r="F51" t="n">
-        <v>140.9190194182076</v>
+        <v>140.4117788809697</v>
       </c>
       <c r="G51" t="n">
         <v>4340800</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>141.6872100830078</v>
+        <v>141.1772155761719</v>
       </c>
       <c r="D52" t="n">
-        <v>142.3955378215411</v>
+        <v>141.882993732033</v>
       </c>
       <c r="E52" t="n">
-        <v>141.4677243891722</v>
+        <v>140.95851990776</v>
       </c>
       <c r="F52" t="n">
-        <v>141.9366242602726</v>
+        <v>141.4257320022546</v>
       </c>
       <c r="G52" t="n">
         <v>2818300</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>139.4923706054688</v>
+        <v>138.9902801513672</v>
       </c>
       <c r="D53" t="n">
-        <v>141.3479974999751</v>
+        <v>140.839227880941</v>
       </c>
       <c r="E53" t="n">
-        <v>139.4724132085181</v>
+        <v>138.9703945893022</v>
       </c>
       <c r="F53" t="n">
-        <v>140.9688982961137</v>
+        <v>140.461493211144</v>
       </c>
       <c r="G53" t="n">
         <v>3503300</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>139.2230072021484</v>
+        <v>138.7218627929688</v>
       </c>
       <c r="D54" t="n">
-        <v>139.8615069347593</v>
+        <v>139.3580641944511</v>
       </c>
       <c r="E54" t="n">
-        <v>137.5768643753149</v>
+        <v>137.0816453896048</v>
       </c>
       <c r="F54" t="n">
-        <v>137.9260503388041</v>
+        <v>137.4295744301408</v>
       </c>
       <c r="G54" t="n">
         <v>5703700</v>
@@ -1691,16 +1691,16 @@
         <v>46101</v>
       </c>
       <c r="C55" t="n">
-        <v>136.3200073242188</v>
+        <v>135.8293151855469</v>
       </c>
       <c r="D55" t="n">
-        <v>138.8200073242188</v>
+        <v>138.3203162838394</v>
       </c>
       <c r="E55" t="n">
-        <v>135.5800018310547</v>
+        <v>135.0919733870612</v>
       </c>
       <c r="F55" t="n">
-        <v>138.6699981689453</v>
+        <v>138.1708470956233</v>
       </c>
       <c r="G55" t="n">
         <v>5287200</v>
@@ -1714,16 +1714,16 @@
         <v>46104</v>
       </c>
       <c r="C56" t="n">
-        <v>138.6000061035156</v>
+        <v>138.1011047363281</v>
       </c>
       <c r="D56" t="n">
-        <v>140.1100006103516</v>
+        <v>139.6056639019611</v>
       </c>
       <c r="E56" t="n">
-        <v>137.8699951171875</v>
+        <v>137.373721480614</v>
       </c>
       <c r="F56" t="n">
-        <v>138.6000061035156</v>
+        <v>138.1011047363281</v>
       </c>
       <c r="G56" t="n">
         <v>6783800</v>
@@ -1737,16 +1737,16 @@
         <v>46105</v>
       </c>
       <c r="C57" t="n">
-        <v>137.8999938964844</v>
+        <v>137.4036254882812</v>
       </c>
       <c r="D57" t="n">
-        <v>138.6999969482422</v>
+        <v>138.2007489442527</v>
       </c>
       <c r="E57" t="n">
-        <v>136.9499969482422</v>
+        <v>136.4570480360062</v>
       </c>
       <c r="F57" t="n">
-        <v>137.3000030517578</v>
+        <v>136.8057942992016</v>
       </c>
       <c r="G57" t="n">
         <v>4429000</v>
@@ -1760,16 +1760,16 @@
         <v>46106</v>
       </c>
       <c r="C58" t="n">
-        <v>139.1699981689453</v>
+        <v>138.6690521240234</v>
       </c>
       <c r="D58" t="n">
-        <v>139.9299926757812</v>
+        <v>139.4263110107734</v>
       </c>
       <c r="E58" t="n">
-        <v>138.5200042724609</v>
+        <v>138.0213978975538</v>
       </c>
       <c r="F58" t="n">
-        <v>139.6499938964844</v>
+        <v>139.1473200943989</v>
       </c>
       <c r="G58" t="n">
         <v>4334000</v>
@@ -1783,16 +1783,16 @@
         <v>46107</v>
       </c>
       <c r="C59" t="n">
-        <v>136.4400024414062</v>
+        <v>135.9488830566406</v>
       </c>
       <c r="D59" t="n">
-        <v>138.6399993896484</v>
+        <v>138.1409610578851</v>
       </c>
       <c r="E59" t="n">
-        <v>136.3399963378906</v>
+        <v>135.8492369277303</v>
       </c>
       <c r="F59" t="n">
-        <v>137.8399963378906</v>
+        <v>137.3438376381967</v>
       </c>
       <c r="G59" t="n">
         <v>4334400</v>
@@ -1806,16 +1806,16 @@
         <v>46108</v>
       </c>
       <c r="C60" t="n">
-        <v>134.6199951171875</v>
+        <v>134.1354217529297</v>
       </c>
       <c r="D60" t="n">
-        <v>136.1100006103516</v>
+        <v>135.6200638751179</v>
       </c>
       <c r="E60" t="n">
-        <v>134.2899932861328</v>
+        <v>133.8066077847727</v>
       </c>
       <c r="F60" t="n">
-        <v>135.8699951171875</v>
+        <v>135.3809222972226</v>
       </c>
       <c r="G60" t="n">
         <v>5289200</v>
@@ -1829,16 +1829,16 @@
         <v>46111</v>
       </c>
       <c r="C61" t="n">
-        <v>134.1900024414062</v>
+        <v>133.7069854736328</v>
       </c>
       <c r="D61" t="n">
-        <v>135.9400024414062</v>
+        <v>135.4506863479288</v>
       </c>
       <c r="E61" t="n">
-        <v>133.6499938964844</v>
+        <v>133.1689206896856</v>
       </c>
       <c r="F61" t="n">
-        <v>135.8399963378906</v>
+        <v>135.351040216423</v>
       </c>
       <c r="G61" t="n">
         <v>4883100</v>
@@ -1852,16 +1852,16 @@
         <v>46112</v>
       </c>
       <c r="C62" t="n">
-        <v>138.3200073242188</v>
+        <v>137.8221282958984</v>
       </c>
       <c r="D62" t="n">
-        <v>138.4799957275391</v>
+        <v>137.9815408254003</v>
       </c>
       <c r="E62" t="n">
-        <v>135.4299926757812</v>
+        <v>134.9425161749971</v>
       </c>
       <c r="F62" t="n">
-        <v>135.7400054931641</v>
+        <v>135.2514131098459</v>
       </c>
       <c r="G62" t="n">
         <v>8261900</v>
@@ -1875,16 +1875,16 @@
         <v>46113</v>
       </c>
       <c r="C63" t="n">
-        <v>139.6900024414062</v>
+        <v>139.1871795654297</v>
       </c>
       <c r="D63" t="n">
-        <v>140.4900054931641</v>
+        <v>139.9843029563081</v>
       </c>
       <c r="E63" t="n">
-        <v>139.2299957275391</v>
+        <v>138.7288286744188</v>
       </c>
       <c r="F63" t="n">
-        <v>139.3399963378906</v>
+        <v>138.8384333307129</v>
       </c>
       <c r="G63" t="n">
         <v>3990700</v>
@@ -1898,16 +1898,16 @@
         <v>46114</v>
       </c>
       <c r="C64" t="n">
-        <v>139.3699951171875</v>
+        <v>138.8683319091797</v>
       </c>
       <c r="D64" t="n">
-        <v>139.9100036621094</v>
+        <v>139.4063966898159</v>
       </c>
       <c r="E64" t="n">
-        <v>136.9799957275391</v>
+        <v>136.4869353379495</v>
       </c>
       <c r="F64" t="n">
-        <v>137.2400054931641</v>
+        <v>136.7460091967243</v>
       </c>
       <c r="G64" t="n">
         <v>2973800</v>
@@ -1921,16 +1921,16 @@
         <v>46118</v>
       </c>
       <c r="C65" t="n">
-        <v>140.0700073242188</v>
+        <v>139.5658264160156</v>
       </c>
       <c r="D65" t="n">
-        <v>140.3099975585938</v>
+        <v>139.8049528073979</v>
       </c>
       <c r="E65" t="n">
-        <v>139.4299926757812</v>
+        <v>138.928115495356</v>
       </c>
       <c r="F65" t="n">
-        <v>139.8600006103516</v>
+        <v>139.356575619691</v>
       </c>
       <c r="G65" t="n">
         <v>2548900</v>
@@ -1944,16 +1944,16 @@
         <v>46119</v>
       </c>
       <c r="C66" t="n">
-        <v>140.1300048828125</v>
+        <v>139.6256103515625</v>
       </c>
       <c r="D66" t="n">
-        <v>140.2599945068359</v>
+        <v>139.755132081108</v>
       </c>
       <c r="E66" t="n">
-        <v>138.2899932861328</v>
+        <v>137.7922218317005</v>
       </c>
       <c r="F66" t="n">
-        <v>139.5200042724609</v>
+        <v>139.0178054235145</v>
       </c>
       <c r="G66" t="n">
         <v>3542000</v>
@@ -1967,16 +1967,16 @@
         <v>46120</v>
       </c>
       <c r="C67" t="n">
-        <v>144.5800018310547</v>
+        <v>144.0595855712891</v>
       </c>
       <c r="D67" t="n">
-        <v>145.2899932861328</v>
+        <v>144.7670214094573</v>
       </c>
       <c r="E67" t="n">
-        <v>143.7299957275391</v>
+        <v>143.2126390679364</v>
       </c>
       <c r="F67" t="n">
-        <v>144.7100067138672</v>
+        <v>144.1891225010375</v>
       </c>
       <c r="G67" t="n">
         <v>6111500</v>
@@ -1990,16 +1990,16 @@
         <v>46121</v>
       </c>
       <c r="C68" t="n">
-        <v>144.9499969482422</v>
+        <v>144.4282531738281</v>
       </c>
       <c r="D68" t="n">
-        <v>145.3500061035156</v>
+        <v>144.8268225064671</v>
       </c>
       <c r="E68" t="n">
-        <v>143.5700073242188</v>
+        <v>143.0532307868537</v>
       </c>
       <c r="F68" t="n">
-        <v>143.8500061035156</v>
+        <v>143.3322217177682</v>
       </c>
       <c r="G68" t="n">
         <v>3965000</v>
@@ -2013,16 +2013,16 @@
         <v>46122</v>
       </c>
       <c r="C69" t="n">
-        <v>144.9799957275391</v>
+        <v>144.4581298828125</v>
       </c>
       <c r="D69" t="n">
-        <v>145.6600036621094</v>
+        <v>145.1356900802766</v>
       </c>
       <c r="E69" t="n">
-        <v>144.7200012207031</v>
+        <v>144.1990712447649</v>
       </c>
       <c r="F69" t="n">
-        <v>145.3800048828125</v>
+        <v>144.8566991765749</v>
       </c>
       <c r="G69" t="n">
         <v>2317400</v>
@@ -2036,16 +2036,16 @@
         <v>46125</v>
       </c>
       <c r="C70" t="n">
-        <v>146.3999938964844</v>
+        <v>145.8730163574219</v>
       </c>
       <c r="D70" t="n">
-        <v>146.4600067138672</v>
+        <v>145.9328131542573</v>
       </c>
       <c r="E70" t="n">
-        <v>144.1699981689453</v>
+        <v>143.6510476634184</v>
       </c>
       <c r="F70" t="n">
-        <v>144.4299926757812</v>
+        <v>143.9101063009163</v>
       </c>
       <c r="G70" t="n">
         <v>4455900</v>
@@ -2059,16 +2059,16 @@
         <v>46126</v>
       </c>
       <c r="C71" t="n">
-        <v>148.0899963378906</v>
+        <v>147.5569458007812</v>
       </c>
       <c r="D71" t="n">
-        <v>148.1799926757812</v>
+        <v>147.6466181964919</v>
       </c>
       <c r="E71" t="n">
-        <v>146.9400024414062</v>
+        <v>146.41109131195</v>
       </c>
       <c r="F71" t="n">
-        <v>146.9400024414062</v>
+        <v>146.41109131195</v>
       </c>
       <c r="G71" t="n">
         <v>3059500</v>
@@ -2082,16 +2082,16 @@
         <v>46127</v>
       </c>
       <c r="C72" t="n">
-        <v>148.6199951171875</v>
+        <v>148.0850372314453</v>
       </c>
       <c r="D72" t="n">
-        <v>148.7100067138672</v>
+        <v>148.1747248312535</v>
       </c>
       <c r="E72" t="n">
-        <v>147.7299957275391</v>
+        <v>147.1982413958773</v>
       </c>
       <c r="F72" t="n">
-        <v>147.8899993896484</v>
+        <v>147.3576691245753</v>
       </c>
       <c r="G72" t="n">
         <v>2622700</v>
@@ -2105,16 +2105,16 @@
         <v>46128</v>
       </c>
       <c r="C73" t="n">
-        <v>148.7899932861328</v>
+        <v>148.2544250488281</v>
       </c>
       <c r="D73" t="n">
-        <v>149.1000061035156</v>
+        <v>148.5633219778741</v>
       </c>
       <c r="E73" t="n">
-        <v>148.3500061035156</v>
+        <v>147.8160215961018</v>
       </c>
       <c r="F73" t="n">
-        <v>148.9299926757812</v>
+        <v>148.3939205119377</v>
       </c>
       <c r="G73" t="n">
         <v>2329000</v>
@@ -2128,16 +2128,16 @@
         <v>46129</v>
       </c>
       <c r="C74" t="n">
-        <v>150.8399963378906</v>
+        <v>150.2970428466797</v>
       </c>
       <c r="D74" t="n">
-        <v>151.4400024414062</v>
+        <v>150.8948892086376</v>
       </c>
       <c r="E74" t="n">
-        <v>150.1300048828125</v>
+        <v>149.5896070290228</v>
       </c>
       <c r="F74" t="n">
-        <v>150.2599945068359</v>
+        <v>149.7191287511509</v>
       </c>
       <c r="G74" t="n">
         <v>3111100</v>
@@ -2151,16 +2151,16 @@
         <v>46132</v>
       </c>
       <c r="C75" t="n">
-        <v>150.4799957275391</v>
+        <v>149.9383392333984</v>
       </c>
       <c r="D75" t="n">
-        <v>150.5800018310547</v>
+        <v>150.0379853624526</v>
       </c>
       <c r="E75" t="n">
-        <v>149.7700042724609</v>
+        <v>149.2309034102538</v>
       </c>
       <c r="F75" t="n">
-        <v>150.25</v>
+        <v>149.7091713812115</v>
       </c>
       <c r="G75" t="n">
         <v>3183300</v>
@@ -2174,16 +2174,16 @@
         <v>46133</v>
       </c>
       <c r="C76" t="n">
-        <v>148.7599945068359</v>
+        <v>148.2245330810547</v>
       </c>
       <c r="D76" t="n">
-        <v>150.6900024414062</v>
+        <v>150.1475939543278</v>
       </c>
       <c r="E76" t="n">
-        <v>148.5200042724609</v>
+        <v>147.9854066912469</v>
       </c>
       <c r="F76" t="n">
-        <v>150.5200042724609</v>
+        <v>149.9782076935922</v>
       </c>
       <c r="G76" t="n">
         <v>2473100</v>
@@ -2197,16 +2197,16 @@
         <v>46134</v>
       </c>
       <c r="C77" t="n">
-        <v>150.1000061035156</v>
+        <v>149.5597229003906</v>
       </c>
       <c r="D77" t="n">
-        <v>150.1300048828125</v>
+        <v>149.5896136994349</v>
       </c>
       <c r="E77" t="n">
-        <v>149.6600036621094</v>
+        <v>149.121304242587</v>
       </c>
       <c r="F77" t="n">
-        <v>149.8600006103516</v>
+        <v>149.3205813041709</v>
       </c>
       <c r="G77" t="n">
         <v>1863900</v>
@@ -2220,16 +2220,16 @@
         <v>46135</v>
       </c>
       <c r="C78" t="n">
-        <v>149.1499938964844</v>
+        <v>148.6131286621094</v>
       </c>
       <c r="D78" t="n">
-        <v>150.1499938964844</v>
+        <v>149.6095291632402</v>
       </c>
       <c r="E78" t="n">
-        <v>147.6999969482422</v>
+        <v>147.1683509762427</v>
       </c>
       <c r="F78" t="n">
-        <v>149.7100067138672</v>
+        <v>149.1711257139893</v>
       </c>
       <c r="G78" t="n">
         <v>3382900</v>
@@ -2243,16 +2243,16 @@
         <v>46136</v>
       </c>
       <c r="C79" t="n">
-        <v>150.3399963378906</v>
+        <v>149.7988433837891</v>
       </c>
       <c r="D79" t="n">
-        <v>150.4199981689453</v>
+        <v>149.8785572460513</v>
       </c>
       <c r="E79" t="n">
-        <v>149.2799987792969</v>
+        <v>148.7426613155781</v>
       </c>
       <c r="F79" t="n">
-        <v>149.7200012207031</v>
+        <v>149.1810799560878</v>
       </c>
       <c r="G79" t="n">
         <v>4861300</v>
@@ -2266,16 +2266,16 @@
         <v>46139</v>
       </c>
       <c r="C80" t="n">
-        <v>150.3200073242188</v>
+        <v>149.7789306640625</v>
       </c>
       <c r="D80" t="n">
-        <v>150.5500030517578</v>
+        <v>150.0080985222958</v>
       </c>
       <c r="E80" t="n">
-        <v>149.9199981689453</v>
+        <v>149.3803613411947</v>
       </c>
       <c r="F80" t="n">
-        <v>150.3500061035156</v>
+        <v>149.8088214627944</v>
       </c>
       <c r="G80" t="n">
         <v>2892900</v>
@@ -2289,16 +2289,16 @@
         <v>46140</v>
       </c>
       <c r="C81" t="n">
-        <v>149.4600067138672</v>
+        <v>148.9220275878906</v>
       </c>
       <c r="D81" t="n">
-        <v>149.8399963378906</v>
+        <v>149.3006494447748</v>
       </c>
       <c r="E81" t="n">
-        <v>148.8899993896484</v>
+        <v>148.3540719967664</v>
       </c>
       <c r="F81" t="n">
-        <v>149.6100006103516</v>
+        <v>149.0714815835206</v>
       </c>
       <c r="G81" t="n">
         <v>1857100</v>
@@ -2312,16 +2312,16 @@
         <v>46141</v>
       </c>
       <c r="C82" t="n">
-        <v>148.9400024414062</v>
+        <v>148.4038848876953</v>
       </c>
       <c r="D82" t="n">
-        <v>149.5099945068359</v>
+        <v>148.9718252360124</v>
       </c>
       <c r="E82" t="n">
-        <v>148.3000030517578</v>
+        <v>147.7661892102903</v>
       </c>
       <c r="F82" t="n">
-        <v>149.5099945068359</v>
+        <v>148.9718252360124</v>
       </c>
       <c r="G82" t="n">
         <v>2203600</v>
@@ -2335,16 +2335,16 @@
         <v>46142</v>
       </c>
       <c r="C83" t="n">
-        <v>151.1999969482422</v>
+        <v>150.6557464599609</v>
       </c>
       <c r="D83" t="n">
-        <v>151.3800048828125</v>
+        <v>150.8351064487094</v>
       </c>
       <c r="E83" t="n">
-        <v>149.3999938964844</v>
+        <v>148.8622225917984</v>
       </c>
       <c r="F83" t="n">
-        <v>149.8399963378906</v>
+        <v>149.3006412266675</v>
       </c>
       <c r="G83" t="n">
         <v>4025100</v>
@@ -2358,16 +2358,16 @@
         <v>46143</v>
       </c>
       <c r="C84" t="n">
-        <v>151.4400024414062</v>
+        <v>150.8948974609375</v>
       </c>
       <c r="D84" t="n">
-        <v>152.3999938964844</v>
+        <v>151.8514334477448</v>
       </c>
       <c r="E84" t="n">
-        <v>151.3300018310547</v>
+        <v>150.7852927953799</v>
       </c>
       <c r="F84" t="n">
-        <v>151.6000061035156</v>
+        <v>151.0543251933605</v>
       </c>
       <c r="G84" t="n">
         <v>2817700</v>
@@ -2381,16 +2381,16 @@
         <v>46146</v>
       </c>
       <c r="C85" t="n">
-        <v>150.5599975585938</v>
+        <v>150.0180511474609</v>
       </c>
       <c r="D85" t="n">
-        <v>151.7200012207031</v>
+        <v>151.173879332473</v>
       </c>
       <c r="E85" t="n">
-        <v>150.0099945068359</v>
+        <v>149.47002785251</v>
       </c>
       <c r="F85" t="n">
-        <v>151.2899932861328</v>
+        <v>150.7454192277424</v>
       </c>
       <c r="G85" t="n">
         <v>2609800</v>
@@ -2404,16 +2404,16 @@
         <v>46147</v>
       </c>
       <c r="C86" t="n">
-        <v>152.1199951171875</v>
+        <v>151.5724334716797</v>
       </c>
       <c r="D86" t="n">
-        <v>152.4299926757812</v>
+        <v>151.8813151823985</v>
       </c>
       <c r="E86" t="n">
-        <v>151.5500030517578</v>
+        <v>151.0044931141339</v>
       </c>
       <c r="F86" t="n">
-        <v>151.6699981689453</v>
+        <v>151.1240563043825</v>
       </c>
       <c r="G86" t="n">
         <v>2451800</v>
@@ -2427,16 +2427,16 @@
         <v>46148</v>
       </c>
       <c r="C87" t="n">
-        <v>155.0599975585938</v>
+        <v>154.5018615722656</v>
       </c>
       <c r="D87" t="n">
-        <v>155.1699981689453</v>
+        <v>154.6114662371759</v>
       </c>
       <c r="E87" t="n">
-        <v>153.9100036621094</v>
+        <v>153.3560070604568</v>
       </c>
       <c r="F87" t="n">
-        <v>154.1300048828125</v>
+        <v>153.5752163902774</v>
       </c>
       <c r="G87" t="n">
         <v>2151100</v>
@@ -2450,16 +2450,16 @@
         <v>46149</v>
       </c>
       <c r="C88" t="n">
-        <v>153.7200012207031</v>
+        <v>153.1666870117188</v>
       </c>
       <c r="D88" t="n">
-        <v>155.3099975585938</v>
+        <v>154.7509601674665</v>
       </c>
       <c r="E88" t="n">
-        <v>153.4499969482422</v>
+        <v>152.8976546179935</v>
       </c>
       <c r="F88" t="n">
-        <v>155.2700042724609</v>
+        <v>154.7111108369238</v>
       </c>
       <c r="G88" t="n">
         <v>2744800</v>
@@ -2473,16 +2473,16 @@
         <v>46150</v>
       </c>
       <c r="C89" t="n">
-        <v>155.1799926757812</v>
+        <v>154.6214141845703</v>
       </c>
       <c r="D89" t="n">
-        <v>155.2700042724609</v>
+        <v>154.711101779805</v>
       </c>
       <c r="E89" t="n">
-        <v>154.6999969482422</v>
+        <v>154.1431462267305</v>
       </c>
       <c r="F89" t="n">
-        <v>154.9400024414062</v>
+        <v>154.3822878075825</v>
       </c>
       <c r="G89" t="n">
         <v>2360700</v>
@@ -2496,16 +2496,16 @@
         <v>46153</v>
       </c>
       <c r="C90" t="n">
-        <v>155.3200073242188</v>
+        <v>154.7609252929688</v>
       </c>
       <c r="D90" t="n">
-        <v>155.6300048828125</v>
+        <v>155.0698070000523</v>
       </c>
       <c r="E90" t="n">
-        <v>155</v>
+        <v>154.4420698509056</v>
       </c>
       <c r="F90" t="n">
-        <v>155.3300018310547</v>
+        <v>154.7708838240841</v>
       </c>
       <c r="G90" t="n">
         <v>2164600</v>
@@ -2519,16 +2519,16 @@
         <v>46154</v>
       </c>
       <c r="C91" t="n">
-        <v>154.3500061035156</v>
+        <v>153.7944183349609</v>
       </c>
       <c r="D91" t="n">
-        <v>154.5099945068359</v>
+        <v>153.9538308549221</v>
       </c>
       <c r="E91" t="n">
-        <v>152.9799957275391</v>
+        <v>152.4293393550167</v>
       </c>
       <c r="F91" t="n">
-        <v>154.2400054931641</v>
+        <v>153.6848136753138</v>
       </c>
       <c r="G91" t="n">
         <v>2307800</v>
@@ -2542,16 +2542,16 @@
         <v>46155</v>
       </c>
       <c r="C92" t="n">
-        <v>155.3999938964844</v>
+        <v>154.8406219482422</v>
       </c>
       <c r="D92" t="n">
-        <v>155.5700073242188</v>
+        <v>155.0100234020638</v>
       </c>
       <c r="E92" t="n">
-        <v>154.0099945068359</v>
+        <v>153.4556259478935</v>
       </c>
       <c r="F92" t="n">
-        <v>154.4199981689453</v>
+        <v>153.8641537763075</v>
       </c>
       <c r="G92" t="n">
         <v>1550500</v>
@@ -2565,16 +2565,16 @@
         <v>46156</v>
       </c>
       <c r="C93" t="n">
-        <v>156.0200042724609</v>
+        <v>155.4584045410156</v>
       </c>
       <c r="D93" t="n">
-        <v>156.4199981689453</v>
+        <v>155.8569586447895</v>
       </c>
       <c r="E93" t="n">
-        <v>155.3500061035156</v>
+        <v>154.7908180550689</v>
       </c>
       <c r="F93" t="n">
-        <v>155.5599975585938</v>
+        <v>155.0000536381976</v>
       </c>
       <c r="G93" t="n">
         <v>2520100</v>
@@ -2588,16 +2588,16 @@
         <v>46157</v>
       </c>
       <c r="C94" t="n">
-        <v>153.5200042724609</v>
+        <v>152.9674072265625</v>
       </c>
       <c r="D94" t="n">
-        <v>154.3000030517578</v>
+        <v>153.7445983911561</v>
       </c>
       <c r="E94" t="n">
-        <v>153.2200012207031</v>
+        <v>152.6684840392885</v>
       </c>
       <c r="F94" t="n">
-        <v>154.1900024414062</v>
+        <v>153.6349937292844</v>
       </c>
       <c r="G94" t="n">
         <v>3071500</v>
@@ -2611,16 +2611,16 @@
         <v>46160</v>
       </c>
       <c r="C95" t="n">
-        <v>153.7100067138672</v>
+        <v>153.1567230224609</v>
       </c>
       <c r="D95" t="n">
-        <v>154.4100036621094</v>
+        <v>153.8542003110936</v>
       </c>
       <c r="E95" t="n">
-        <v>152.6100006103516</v>
+        <v>152.0606764232778</v>
       </c>
       <c r="F95" t="n">
-        <v>154.0200042724609</v>
+        <v>153.4656047357222</v>
       </c>
       <c r="G95" t="n">
         <v>2650000</v>
@@ -2634,16 +2634,16 @@
         <v>46161</v>
       </c>
       <c r="C96" t="n">
-        <v>152.6300048828125</v>
+        <v>152.0806121826172</v>
       </c>
       <c r="D96" t="n">
-        <v>153.5</v>
+        <v>152.9474757466939</v>
       </c>
       <c r="E96" t="n">
-        <v>152.0299987792969</v>
+        <v>151.4827658049929</v>
       </c>
       <c r="F96" t="n">
-        <v>152.7200012207031</v>
+        <v>152.1702845781013</v>
       </c>
       <c r="G96" t="n">
         <v>2543900</v>
@@ -2657,16 +2657,16 @@
         <v>46162</v>
       </c>
       <c r="C97" t="n">
-        <v>154.6300048828125</v>
+        <v>154.0734100341797</v>
       </c>
       <c r="D97" t="n">
-        <v>154.7700042724609</v>
+        <v>154.2129054922713</v>
       </c>
       <c r="E97" t="n">
-        <v>152.7200012207031</v>
+        <v>152.1702814814645</v>
       </c>
       <c r="F97" t="n">
-        <v>152.9400024414062</v>
+        <v>152.3894908018749</v>
       </c>
       <c r="G97" t="n">
         <v>2038400</v>
@@ -2680,16 +2680,16 @@
         <v>46163</v>
       </c>
       <c r="C98" t="n">
-        <v>155.2100067138672</v>
+        <v>154.6513214111328</v>
       </c>
       <c r="D98" t="n">
-        <v>155.7100067138672</v>
+        <v>155.1495216389578</v>
       </c>
       <c r="E98" t="n">
-        <v>153.7200012207031</v>
+        <v>153.1666792588232</v>
       </c>
       <c r="F98" t="n">
-        <v>154.1100006103516</v>
+        <v>153.5552748283721</v>
       </c>
       <c r="G98" t="n">
         <v>2375200</v>
@@ -2703,16 +2703,16 @@
         <v>46164</v>
       </c>
       <c r="C99" t="n">
-        <v>155.5700073242188</v>
+        <v>155.0100250244141</v>
       </c>
       <c r="D99" t="n">
-        <v>156.2899932861328</v>
+        <v>155.7274193595633</v>
       </c>
       <c r="E99" t="n">
-        <v>155.3200073242188</v>
+        <v>154.7609249123639</v>
       </c>
       <c r="F99" t="n">
-        <v>155.6999969482422</v>
+        <v>155.1395467440524</v>
       </c>
       <c r="G99" t="n">
         <v>2565600</v>
@@ -2726,16 +2726,16 @@
         <v>46168</v>
       </c>
       <c r="C100" t="n">
-        <v>157.3800048828125</v>
+        <v>156.8135070800781</v>
       </c>
       <c r="D100" t="n">
-        <v>157.6300048828125</v>
+        <v>157.0626071916153</v>
       </c>
       <c r="E100" t="n">
-        <v>156.8999938964844</v>
+        <v>156.3352239191446</v>
       </c>
       <c r="F100" t="n">
-        <v>157.3800048828125</v>
+        <v>156.8135070800781</v>
       </c>
       <c r="G100" t="n">
         <v>2407900</v>
@@ -2749,16 +2749,16 @@
         <v>46169</v>
       </c>
       <c r="C101" t="n">
-        <v>157.1600036621094</v>
+        <v>156.5942993164062</v>
       </c>
       <c r="D101" t="n">
-        <v>157.5899963378906</v>
+        <v>157.0227442146382</v>
       </c>
       <c r="E101" t="n">
-        <v>156.7299957275391</v>
+        <v>156.1658392143099</v>
       </c>
       <c r="F101" t="n">
-        <v>157.5</v>
+        <v>156.9330718225243</v>
       </c>
       <c r="G101" t="n">
         <v>4252100</v>
@@ -2772,16 +2772,16 @@
         <v>46170</v>
       </c>
       <c r="C102" t="n">
-        <v>157.8699951171875</v>
+        <v>157.3017425537109</v>
       </c>
       <c r="D102" t="n">
-        <v>158.0099945068359</v>
+        <v>157.4412380159855</v>
       </c>
       <c r="E102" t="n">
-        <v>156.4700012207031</v>
+        <v>155.9067879309653</v>
       </c>
       <c r="F102" t="n">
-        <v>156.7200012207031</v>
+        <v>156.1558880567317</v>
       </c>
       <c r="G102" t="n">
         <v>3263200</v>
@@ -2795,16 +2795,16 @@
         <v>46171</v>
       </c>
       <c r="C103" t="n">
-        <v>158.1199951171875</v>
+        <v>157.5508422851562</v>
       </c>
       <c r="D103" t="n">
-        <v>158.5299987792969</v>
+        <v>157.9593701393183</v>
       </c>
       <c r="E103" t="n">
-        <v>157.8000030517578</v>
+        <v>157.2320020309832</v>
       </c>
       <c r="F103" t="n">
-        <v>158.1399993896484</v>
+        <v>157.5707745522499</v>
       </c>
       <c r="G103" t="n">
         <v>5118100</v>
@@ -2818,16 +2818,16 @@
         <v>46174</v>
       </c>
       <c r="C104" t="n">
-        <v>158.6000061035156</v>
+        <v>158.0291290283203</v>
       </c>
       <c r="D104" t="n">
-        <v>159.1699981689453</v>
+        <v>158.5970694204166</v>
       </c>
       <c r="E104" t="n">
-        <v>157.5</v>
+        <v>156.9330823714813</v>
       </c>
       <c r="F104" t="n">
-        <v>158.0399932861328</v>
+        <v>157.471131964197</v>
       </c>
       <c r="G104" t="n">
         <v>3407100</v>
@@ -2841,16 +2841,16 @@
         <v>46175</v>
       </c>
       <c r="C105" t="n">
-        <v>159.3500061035156</v>
+        <v>158.7764282226562</v>
       </c>
       <c r="D105" t="n">
-        <v>159.4100036621094</v>
+        <v>158.8362098209664</v>
       </c>
       <c r="E105" t="n">
-        <v>158.4199981689453</v>
+        <v>157.8497678372536</v>
       </c>
       <c r="F105" t="n">
-        <v>158.6499938964844</v>
+        <v>158.0789356987308</v>
       </c>
       <c r="G105" t="n">
         <v>2967600</v>
@@ -2864,16 +2864,16 @@
         <v>46176</v>
       </c>
       <c r="C106" t="n">
-        <v>157.9499969482422</v>
+        <v>157.3814544677734</v>
       </c>
       <c r="D106" t="n">
-        <v>159</v>
+        <v>158.4276780237979</v>
       </c>
       <c r="E106" t="n">
-        <v>157.8099975585938</v>
+        <v>157.2419590072278</v>
       </c>
       <c r="F106" t="n">
-        <v>159</v>
+        <v>158.4276780237979</v>
       </c>
       <c r="G106" t="n">
         <v>3336600</v>
@@ -2887,16 +2887,16 @@
         <v>46177</v>
       </c>
       <c r="C107" t="n">
-        <v>158.5399932861328</v>
+        <v>157.9693298339844</v>
       </c>
       <c r="D107" t="n">
-        <v>158.75</v>
+        <v>158.1785806303457</v>
       </c>
       <c r="E107" t="n">
-        <v>157.4600067138672</v>
+        <v>156.8932306648454</v>
       </c>
       <c r="F107" t="n">
-        <v>157.5700073242188</v>
+        <v>157.0028353288699</v>
       </c>
       <c r="G107" t="n">
         <v>2216100</v>
@@ -2910,16 +2910,16 @@
         <v>46178</v>
       </c>
       <c r="C108" t="n">
-        <v>153.6799926757812</v>
+        <v>153.1268157958984</v>
       </c>
       <c r="D108" t="n">
-        <v>157.0899963378906</v>
+        <v>156.5245450223227</v>
       </c>
       <c r="E108" t="n">
-        <v>153.2299957275391</v>
+        <v>152.6784386284973</v>
       </c>
       <c r="F108" t="n">
-        <v>157.0899963378906</v>
+        <v>156.5245450223227</v>
       </c>
       <c r="G108" t="n">
         <v>3986400</v>
@@ -2933,16 +2933,16 @@
         <v>46181</v>
       </c>
       <c r="C109" t="n">
-        <v>154.4799957275391</v>
+        <v>153.9239349365234</v>
       </c>
       <c r="D109" t="n">
-        <v>155.6000061035156</v>
+        <v>155.0399137623133</v>
       </c>
       <c r="E109" t="n">
-        <v>154.2100067138672</v>
+        <v>153.6549177658646</v>
       </c>
       <c r="F109" t="n">
-        <v>155.1600036621094</v>
+        <v>154.6014951383099</v>
       </c>
       <c r="G109" t="n">
         <v>5059000</v>
@@ -2956,16 +2956,16 @@
         <v>46182</v>
       </c>
       <c r="C110" t="n">
-        <v>154.3000030517578</v>
+        <v>153.7445983886719</v>
       </c>
       <c r="D110" t="n">
-        <v>156.5599975585938</v>
+        <v>155.9964580188855</v>
       </c>
       <c r="E110" t="n">
-        <v>151.1999969482422</v>
+        <v>150.6557507933315</v>
       </c>
       <c r="F110" t="n">
-        <v>155.7400054931641</v>
+        <v>155.1794175244722</v>
       </c>
       <c r="G110" t="n">
         <v>5115600</v>
@@ -2979,16 +2979,16 @@
         <v>46183</v>
       </c>
       <c r="C111" t="n">
-        <v>151.9199981689453</v>
+        <v>151.3731536865234</v>
       </c>
       <c r="D111" t="n">
-        <v>154.5700073242188</v>
+        <v>154.0136239864625</v>
       </c>
       <c r="E111" t="n">
-        <v>151.8800048828125</v>
+        <v>151.3333043584483</v>
       </c>
       <c r="F111" t="n">
-        <v>153.3699951171875</v>
+        <v>152.817931290109</v>
       </c>
       <c r="G111" t="n">
         <v>5763500</v>
@@ -3002,16 +3002,16 @@
         <v>46184</v>
       </c>
       <c r="C112" t="n">
-        <v>155.6100006103516</v>
+        <v>155.0498809814453</v>
       </c>
       <c r="D112" t="n">
-        <v>155.8800048828125</v>
+        <v>155.3189133710433</v>
       </c>
       <c r="E112" t="n">
-        <v>152.2400054931641</v>
+        <v>151.6920161926882</v>
       </c>
       <c r="F112" t="n">
-        <v>152.9199981689453</v>
+        <v>152.3695612285766</v>
       </c>
       <c r="G112" t="n">
         <v>4852900</v>
@@ -3025,19 +3025,134 @@
         <v>46185</v>
       </c>
       <c r="C113" t="n">
-        <v>156.2899932861328</v>
+        <v>155.7274169921875</v>
       </c>
       <c r="D113" t="n">
-        <v>156.8399963378906</v>
+        <v>156.2754402711396</v>
       </c>
       <c r="E113" t="n">
-        <v>154.9199981689453</v>
+        <v>154.3623532641411</v>
       </c>
       <c r="F113" t="n">
-        <v>155.8999938964844</v>
+        <v>155.3388214314513</v>
       </c>
       <c r="G113" t="n">
-        <v>8976000</v>
+        <v>8980200</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C114" t="n">
+        <v>158.148681640625</v>
+      </c>
+      <c r="D114" t="n">
+        <v>158.6269496025681</v>
+      </c>
+      <c r="E114" t="n">
+        <v>157.9294723239293</v>
+      </c>
+      <c r="F114" t="n">
+        <v>158.1885309691768</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4689200</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C115" t="n">
+        <v>157.4213104248047</v>
+      </c>
+      <c r="D115" t="n">
+        <v>158.5970556419361</v>
+      </c>
+      <c r="E115" t="n">
+        <v>157.3515550963999</v>
+      </c>
+      <c r="F115" t="n">
+        <v>158.3180647360451</v>
+      </c>
+      <c r="G115" t="n">
+        <v>6737700</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C116" t="n">
+        <v>155.8470001220703</v>
+      </c>
+      <c r="D116" t="n">
+        <v>158.2881782165138</v>
+      </c>
+      <c r="E116" t="n">
+        <v>155.5680092086404</v>
+      </c>
+      <c r="F116" t="n">
+        <v>157.8896241127182</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3620600</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C117" t="n">
+        <v>157.6600036621094</v>
+      </c>
+      <c r="D117" t="n">
+        <v>157.9499969482422</v>
+      </c>
+      <c r="E117" t="n">
+        <v>157.1199951171875</v>
+      </c>
+      <c r="F117" t="n">
+        <v>157.7899932861328</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1976600</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C118" t="n">
+        <v>157.5599975585938</v>
+      </c>
+      <c r="D118" t="n">
+        <v>158.4275054931641</v>
+      </c>
+      <c r="E118" t="n">
+        <v>157.2700042724609</v>
+      </c>
+      <c r="F118" t="n">
+        <v>157.8899993896484</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2678303</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>141.2567443847656</v>
+        <v>141.2567291259766</v>
       </c>
       <c r="D2" t="n">
-        <v>141.6245438460415</v>
+        <v>141.6245285475221</v>
       </c>
       <c r="E2" t="n">
-        <v>140.5410158554122</v>
+        <v>140.5410006739373</v>
       </c>
       <c r="F2" t="n">
-        <v>141.4157833715471</v>
+        <v>141.4157680955784</v>
       </c>
       <c r="G2" t="n">
         <v>4387700</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>143.2846374511719</v>
+        <v>143.2846221923828</v>
       </c>
       <c r="D4" t="n">
-        <v>143.364164531834</v>
+        <v>143.3641492645759</v>
       </c>
       <c r="E4" t="n">
-        <v>142.6385007771216</v>
+        <v>142.6384855871414</v>
       </c>
       <c r="F4" t="n">
-        <v>142.6981422955583</v>
+        <v>142.6981270992267</v>
       </c>
       <c r="G4" t="n">
         <v>4700600</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>145.9288482666016</v>
+        <v>145.9288330078125</v>
       </c>
       <c r="D19" t="n">
-        <v>146.3861099958698</v>
+        <v>146.386094689268</v>
       </c>
       <c r="E19" t="n">
-        <v>145.451700976162</v>
+        <v>145.451685767265</v>
       </c>
       <c r="F19" t="n">
-        <v>146.2767621617859</v>
+        <v>146.2767468666178</v>
       </c>
       <c r="G19" t="n">
         <v>4430300</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>144.7459106445312</v>
+        <v>144.7458953857422</v>
       </c>
       <c r="D23" t="n">
-        <v>145.6902700484627</v>
+        <v>145.6902546901213</v>
       </c>
       <c r="E23" t="n">
-        <v>143.5331492480756</v>
+        <v>143.5331341171332</v>
       </c>
       <c r="F23" t="n">
-        <v>145.5809222121186</v>
+        <v>145.5809068653045</v>
       </c>
       <c r="G23" t="n">
         <v>5718700</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>146.7936706542969</v>
+        <v>146.7936859130859</v>
       </c>
       <c r="D27" t="n">
-        <v>147.0521222591024</v>
+        <v>147.0521375447568</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4516911465814</v>
+        <v>145.4517062658755</v>
       </c>
       <c r="F27" t="n">
-        <v>145.6007949246927</v>
+        <v>145.6008100594857</v>
       </c>
       <c r="G27" t="n">
         <v>3890200</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>146.7042083740234</v>
+        <v>146.7042236328125</v>
       </c>
       <c r="D28" t="n">
-        <v>147.4199368453681</v>
+        <v>147.4199521786005</v>
       </c>
       <c r="E28" t="n">
-        <v>146.6644372543722</v>
+        <v>146.6644525090246</v>
       </c>
       <c r="F28" t="n">
-        <v>147.3404097743034</v>
+        <v>147.3404250992641</v>
       </c>
       <c r="G28" t="n">
         <v>3727000</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>146.8235015869141</v>
+        <v>146.823486328125</v>
       </c>
       <c r="D37" t="n">
-        <v>147.0024413012886</v>
+        <v>147.0024260239031</v>
       </c>
       <c r="E37" t="n">
-        <v>145.4715716214576</v>
+        <v>145.4715565031693</v>
       </c>
       <c r="F37" t="n">
-        <v>145.7300384124165</v>
+        <v>145.7300232672668</v>
       </c>
       <c r="G37" t="n">
         <v>6002800</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>146.0779571533203</v>
+        <v>146.0779418945312</v>
       </c>
       <c r="D41" t="n">
-        <v>146.5849403873314</v>
+        <v>146.5849250755847</v>
       </c>
       <c r="E41" t="n">
-        <v>144.4377547530523</v>
+        <v>144.437739665593</v>
       </c>
       <c r="F41" t="n">
-        <v>144.6067441083095</v>
+        <v>144.6067290031982</v>
       </c>
       <c r="G41" t="n">
         <v>7713300</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>144.3979644775391</v>
+        <v>144.3979797363281</v>
       </c>
       <c r="D43" t="n">
-        <v>144.7260079477315</v>
+        <v>144.7260232411855</v>
       </c>
       <c r="E43" t="n">
-        <v>143.0659202057788</v>
+        <v>143.0659353238083</v>
       </c>
       <c r="F43" t="n">
-        <v>143.6225945182615</v>
+        <v>143.6226096951158</v>
       </c>
       <c r="G43" t="n">
         <v>5318000</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>142.718017578125</v>
+        <v>142.7180023193359</v>
       </c>
       <c r="D44" t="n">
-        <v>144.0003556368688</v>
+        <v>144.0003402409777</v>
       </c>
       <c r="E44" t="n">
-        <v>141.4555499119358</v>
+        <v>141.4555347881243</v>
       </c>
       <c r="F44" t="n">
-        <v>143.155393737904</v>
+        <v>143.1553784323526</v>
       </c>
       <c r="G44" t="n">
         <v>10527800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>141.0877380371094</v>
+        <v>141.0877227783203</v>
       </c>
       <c r="D45" t="n">
-        <v>141.7835961642497</v>
+        <v>141.7835808302028</v>
       </c>
       <c r="E45" t="n">
-        <v>140.1930849711274</v>
+        <v>140.193069809096</v>
       </c>
       <c r="F45" t="n">
-        <v>140.8491719759083</v>
+        <v>140.8491567429204</v>
       </c>
       <c r="G45" t="n">
         <v>7498700</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>141.1772155761719</v>
+        <v>141.1772003173828</v>
       </c>
       <c r="D52" t="n">
-        <v>141.882993732033</v>
+        <v>141.8829783969616</v>
       </c>
       <c r="E52" t="n">
-        <v>140.95851990776</v>
+        <v>140.9585046726081</v>
       </c>
       <c r="F52" t="n">
-        <v>141.4257320022546</v>
+        <v>141.4257167166052</v>
       </c>
       <c r="G52" t="n">
         <v>2818300</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>138.9902801513672</v>
+        <v>138.9902648925781</v>
       </c>
       <c r="D53" t="n">
-        <v>140.839227880941</v>
+        <v>140.8392124191687</v>
       </c>
       <c r="E53" t="n">
-        <v>138.9703945893022</v>
+        <v>138.9703793326962</v>
       </c>
       <c r="F53" t="n">
-        <v>140.461493211144</v>
+        <v>140.4614777908405</v>
       </c>
       <c r="G53" t="n">
         <v>3503300</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>138.7218627929688</v>
+        <v>138.7218780517578</v>
       </c>
       <c r="D54" t="n">
-        <v>139.3580641944511</v>
+        <v>139.3580795232195</v>
       </c>
       <c r="E54" t="n">
-        <v>137.0816453896048</v>
+        <v>137.0816604679772</v>
       </c>
       <c r="F54" t="n">
-        <v>137.4295744301408</v>
+        <v>137.4295895467839</v>
       </c>
       <c r="G54" t="n">
         <v>5703700</v>
@@ -3152,7 +3152,7 @@
         <v>157.8899993896484</v>
       </c>
       <c r="G118" t="n">
-        <v>2678303</v>
+        <v>2717444</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>141.2567291259766</v>
+        <v>141.2567443847656</v>
       </c>
       <c r="D2" t="n">
-        <v>141.6245285475221</v>
+        <v>141.6245438460415</v>
       </c>
       <c r="E2" t="n">
-        <v>140.5410006739373</v>
+        <v>140.5410158554122</v>
       </c>
       <c r="F2" t="n">
-        <v>141.4157680955784</v>
+        <v>141.4157833715471</v>
       </c>
       <c r="G2" t="n">
         <v>4387700</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>143.2846221923828</v>
+        <v>143.2846374511719</v>
       </c>
       <c r="D4" t="n">
-        <v>143.3641492645759</v>
+        <v>143.364164531834</v>
       </c>
       <c r="E4" t="n">
-        <v>142.6384855871414</v>
+        <v>142.6385007771216</v>
       </c>
       <c r="F4" t="n">
-        <v>142.6981270992267</v>
+        <v>142.6981422955583</v>
       </c>
       <c r="G4" t="n">
         <v>4700600</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>145.9288330078125</v>
+        <v>145.9288482666016</v>
       </c>
       <c r="D19" t="n">
-        <v>146.386094689268</v>
+        <v>146.3861099958698</v>
       </c>
       <c r="E19" t="n">
-        <v>145.451685767265</v>
+        <v>145.451700976162</v>
       </c>
       <c r="F19" t="n">
-        <v>146.2767468666178</v>
+        <v>146.2767621617859</v>
       </c>
       <c r="G19" t="n">
         <v>4430300</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>144.7458953857422</v>
+        <v>144.7459106445312</v>
       </c>
       <c r="D23" t="n">
-        <v>145.6902546901213</v>
+        <v>145.6902700484627</v>
       </c>
       <c r="E23" t="n">
-        <v>143.5331341171332</v>
+        <v>143.5331492480756</v>
       </c>
       <c r="F23" t="n">
-        <v>145.5809068653045</v>
+        <v>145.5809222121186</v>
       </c>
       <c r="G23" t="n">
         <v>5718700</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>146.7936859130859</v>
+        <v>146.7936706542969</v>
       </c>
       <c r="D27" t="n">
-        <v>147.0521375447568</v>
+        <v>147.0521222591024</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4517062658755</v>
+        <v>145.4516911465814</v>
       </c>
       <c r="F27" t="n">
-        <v>145.6008100594857</v>
+        <v>145.6007949246927</v>
       </c>
       <c r="G27" t="n">
         <v>3890200</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>146.7042236328125</v>
+        <v>146.7042083740234</v>
       </c>
       <c r="D28" t="n">
-        <v>147.4199521786005</v>
+        <v>147.4199368453681</v>
       </c>
       <c r="E28" t="n">
-        <v>146.6644525090246</v>
+        <v>146.6644372543722</v>
       </c>
       <c r="F28" t="n">
-        <v>147.3404250992641</v>
+        <v>147.3404097743034</v>
       </c>
       <c r="G28" t="n">
         <v>3727000</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>146.823486328125</v>
+        <v>146.8235015869141</v>
       </c>
       <c r="D37" t="n">
-        <v>147.0024260239031</v>
+        <v>147.0024413012886</v>
       </c>
       <c r="E37" t="n">
-        <v>145.4715565031693</v>
+        <v>145.4715716214576</v>
       </c>
       <c r="F37" t="n">
-        <v>145.7300232672668</v>
+        <v>145.7300384124165</v>
       </c>
       <c r="G37" t="n">
         <v>6002800</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>146.0779418945312</v>
+        <v>146.0779571533203</v>
       </c>
       <c r="D41" t="n">
-        <v>146.5849250755847</v>
+        <v>146.5849403873314</v>
       </c>
       <c r="E41" t="n">
-        <v>144.437739665593</v>
+        <v>144.4377547530523</v>
       </c>
       <c r="F41" t="n">
-        <v>144.6067290031982</v>
+        <v>144.6067441083095</v>
       </c>
       <c r="G41" t="n">
         <v>7713300</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>144.3979797363281</v>
+        <v>144.3979644775391</v>
       </c>
       <c r="D43" t="n">
-        <v>144.7260232411855</v>
+        <v>144.7260079477315</v>
       </c>
       <c r="E43" t="n">
-        <v>143.0659353238083</v>
+        <v>143.0659202057788</v>
       </c>
       <c r="F43" t="n">
-        <v>143.6226096951158</v>
+        <v>143.6225945182615</v>
       </c>
       <c r="G43" t="n">
         <v>5318000</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>142.7180023193359</v>
+        <v>142.718017578125</v>
       </c>
       <c r="D44" t="n">
-        <v>144.0003402409777</v>
+        <v>144.0003556368688</v>
       </c>
       <c r="E44" t="n">
-        <v>141.4555347881243</v>
+        <v>141.4555499119358</v>
       </c>
       <c r="F44" t="n">
-        <v>143.1553784323526</v>
+        <v>143.155393737904</v>
       </c>
       <c r="G44" t="n">
         <v>10527800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>141.0877227783203</v>
+        <v>141.0877380371094</v>
       </c>
       <c r="D45" t="n">
-        <v>141.7835808302028</v>
+        <v>141.7835961642497</v>
       </c>
       <c r="E45" t="n">
-        <v>140.193069809096</v>
+        <v>140.1930849711274</v>
       </c>
       <c r="F45" t="n">
-        <v>140.8491567429204</v>
+        <v>140.8491719759083</v>
       </c>
       <c r="G45" t="n">
         <v>7498700</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>141.1772003173828</v>
+        <v>141.1772155761719</v>
       </c>
       <c r="D52" t="n">
-        <v>141.8829783969616</v>
+        <v>141.882993732033</v>
       </c>
       <c r="E52" t="n">
-        <v>140.9585046726081</v>
+        <v>140.95851990776</v>
       </c>
       <c r="F52" t="n">
-        <v>141.4257167166052</v>
+        <v>141.4257320022546</v>
       </c>
       <c r="G52" t="n">
         <v>2818300</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>138.9902648925781</v>
+        <v>138.9902801513672</v>
       </c>
       <c r="D53" t="n">
-        <v>140.8392124191687</v>
+        <v>140.839227880941</v>
       </c>
       <c r="E53" t="n">
-        <v>138.9703793326962</v>
+        <v>138.9703945893022</v>
       </c>
       <c r="F53" t="n">
-        <v>140.4614777908405</v>
+        <v>140.461493211144</v>
       </c>
       <c r="G53" t="n">
         <v>3503300</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>138.7218780517578</v>
+        <v>138.7218627929688</v>
       </c>
       <c r="D54" t="n">
-        <v>139.3580795232195</v>
+        <v>139.3580641944511</v>
       </c>
       <c r="E54" t="n">
-        <v>137.0816604679772</v>
+        <v>137.0816453896048</v>
       </c>
       <c r="F54" t="n">
-        <v>137.4295895467839</v>
+        <v>137.4295744301408</v>
       </c>
       <c r="G54" t="n">
         <v>5703700</v>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3143,7 +3143,7 @@
         <v>157.5599975585938</v>
       </c>
       <c r="D118" t="n">
-        <v>158.4275054931641</v>
+        <v>158.4299926757812</v>
       </c>
       <c r="E118" t="n">
         <v>157.2700042724609</v>
@@ -3152,7 +3152,214 @@
         <v>157.8899993896484</v>
       </c>
       <c r="G118" t="n">
-        <v>2717444</v>
+        <v>2718900</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C119" t="n">
+        <v>154.3300018310547</v>
+      </c>
+      <c r="D119" t="n">
+        <v>155.6000061035156</v>
+      </c>
+      <c r="E119" t="n">
+        <v>154.2100067138672</v>
+      </c>
+      <c r="F119" t="n">
+        <v>154.4199981689453</v>
+      </c>
+      <c r="G119" t="n">
+        <v>3432200</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C120" t="n">
+        <v>154.2599945068359</v>
+      </c>
+      <c r="D120" t="n">
+        <v>155.3399963378906</v>
+      </c>
+      <c r="E120" t="n">
+        <v>153.6699981689453</v>
+      </c>
+      <c r="F120" t="n">
+        <v>154.5800018310547</v>
+      </c>
+      <c r="G120" t="n">
+        <v>3436800</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C121" t="n">
+        <v>154.8500061035156</v>
+      </c>
+      <c r="D121" t="n">
+        <v>156.6900024414062</v>
+      </c>
+      <c r="E121" t="n">
+        <v>154</v>
+      </c>
+      <c r="F121" t="n">
+        <v>155.8399963378906</v>
+      </c>
+      <c r="G121" t="n">
+        <v>3836700</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C122" t="n">
+        <v>153.9499969482422</v>
+      </c>
+      <c r="D122" t="n">
+        <v>155.1399993896484</v>
+      </c>
+      <c r="E122" t="n">
+        <v>153.2599945068359</v>
+      </c>
+      <c r="F122" t="n">
+        <v>153.6199951171875</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4824200</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C123" t="n">
+        <v>155.8300018310547</v>
+      </c>
+      <c r="D123" t="n">
+        <v>155.9100036621094</v>
+      </c>
+      <c r="E123" t="n">
+        <v>153.8800048828125</v>
+      </c>
+      <c r="F123" t="n">
+        <v>155.1600036621094</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2903400</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C124" t="n">
+        <v>156.9499969482422</v>
+      </c>
+      <c r="D124" t="n">
+        <v>157.1999969482422</v>
+      </c>
+      <c r="E124" t="n">
+        <v>155.8600006103516</v>
+      </c>
+      <c r="F124" t="n">
+        <v>155.9900054931641</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3835400</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C125" t="n">
+        <v>156.1199951171875</v>
+      </c>
+      <c r="D125" t="n">
+        <v>156.9900054931641</v>
+      </c>
+      <c r="E125" t="n">
+        <v>155.6999969482422</v>
+      </c>
+      <c r="F125" t="n">
+        <v>156.1900024414062</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3083300</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C126" t="n">
+        <v>156.1699981689453</v>
+      </c>
+      <c r="D126" t="n">
+        <v>157.7899932861328</v>
+      </c>
+      <c r="E126" t="n">
+        <v>154.9799957275391</v>
+      </c>
+      <c r="F126" t="n">
+        <v>156.7799987792969</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2264400</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C127" t="n">
+        <v>157.8099975585938</v>
+      </c>
+      <c r="D127" t="n">
+        <v>158.0399932861328</v>
+      </c>
+      <c r="E127" t="n">
+        <v>157.0599975585938</v>
+      </c>
+      <c r="F127" t="n">
+        <v>157.2599945068359</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2571661</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>141.2567443847656</v>
+        <v>141.2567291259766</v>
       </c>
       <c r="D2" t="n">
-        <v>141.6245438460415</v>
+        <v>141.6245285475221</v>
       </c>
       <c r="E2" t="n">
-        <v>140.5410158554122</v>
+        <v>140.5410006739373</v>
       </c>
       <c r="F2" t="n">
-        <v>141.4157833715471</v>
+        <v>141.4157680955784</v>
       </c>
       <c r="G2" t="n">
         <v>4387700</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>143.2846374511719</v>
+        <v>143.2846221923828</v>
       </c>
       <c r="D4" t="n">
-        <v>143.364164531834</v>
+        <v>143.3641492645759</v>
       </c>
       <c r="E4" t="n">
-        <v>142.6385007771216</v>
+        <v>142.6384855871414</v>
       </c>
       <c r="F4" t="n">
-        <v>142.6981422955583</v>
+        <v>142.6981270992267</v>
       </c>
       <c r="G4" t="n">
         <v>4700600</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>145.9288482666016</v>
+        <v>145.9288330078125</v>
       </c>
       <c r="D19" t="n">
-        <v>146.3861099958698</v>
+        <v>146.386094689268</v>
       </c>
       <c r="E19" t="n">
-        <v>145.451700976162</v>
+        <v>145.451685767265</v>
       </c>
       <c r="F19" t="n">
-        <v>146.2767621617859</v>
+        <v>146.2767468666178</v>
       </c>
       <c r="G19" t="n">
         <v>4430300</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>144.7459106445312</v>
+        <v>144.7458953857422</v>
       </c>
       <c r="D23" t="n">
-        <v>145.6902700484627</v>
+        <v>145.6902546901213</v>
       </c>
       <c r="E23" t="n">
-        <v>143.5331492480756</v>
+        <v>143.5331341171332</v>
       </c>
       <c r="F23" t="n">
-        <v>145.5809222121186</v>
+        <v>145.5809068653045</v>
       </c>
       <c r="G23" t="n">
         <v>5718700</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>146.7936706542969</v>
+        <v>146.7936859130859</v>
       </c>
       <c r="D27" t="n">
-        <v>147.0521222591024</v>
+        <v>147.0521375447568</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4516911465814</v>
+        <v>145.4517062658755</v>
       </c>
       <c r="F27" t="n">
-        <v>145.6007949246927</v>
+        <v>145.6008100594857</v>
       </c>
       <c r="G27" t="n">
         <v>3890200</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>146.7042083740234</v>
+        <v>146.7042236328125</v>
       </c>
       <c r="D28" t="n">
-        <v>147.4199368453681</v>
+        <v>147.4199521786005</v>
       </c>
       <c r="E28" t="n">
-        <v>146.6644372543722</v>
+        <v>146.6644525090246</v>
       </c>
       <c r="F28" t="n">
-        <v>147.3404097743034</v>
+        <v>147.3404250992641</v>
       </c>
       <c r="G28" t="n">
         <v>3727000</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>146.8235015869141</v>
+        <v>146.823486328125</v>
       </c>
       <c r="D37" t="n">
-        <v>147.0024413012886</v>
+        <v>147.0024260239031</v>
       </c>
       <c r="E37" t="n">
-        <v>145.4715716214576</v>
+        <v>145.4715565031693</v>
       </c>
       <c r="F37" t="n">
-        <v>145.7300384124165</v>
+        <v>145.7300232672668</v>
       </c>
       <c r="G37" t="n">
         <v>6002800</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>146.0779571533203</v>
+        <v>146.0779418945312</v>
       </c>
       <c r="D41" t="n">
-        <v>146.5849403873314</v>
+        <v>146.5849250755847</v>
       </c>
       <c r="E41" t="n">
-        <v>144.4377547530523</v>
+        <v>144.437739665593</v>
       </c>
       <c r="F41" t="n">
-        <v>144.6067441083095</v>
+        <v>144.6067290031982</v>
       </c>
       <c r="G41" t="n">
         <v>7713300</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>144.3979644775391</v>
+        <v>144.3979797363281</v>
       </c>
       <c r="D43" t="n">
-        <v>144.7260079477315</v>
+        <v>144.7260232411855</v>
       </c>
       <c r="E43" t="n">
-        <v>143.0659202057788</v>
+        <v>143.0659353238083</v>
       </c>
       <c r="F43" t="n">
-        <v>143.6225945182615</v>
+        <v>143.6226096951158</v>
       </c>
       <c r="G43" t="n">
         <v>5318000</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>142.718017578125</v>
+        <v>142.7180023193359</v>
       </c>
       <c r="D44" t="n">
-        <v>144.0003556368688</v>
+        <v>144.0003402409777</v>
       </c>
       <c r="E44" t="n">
-        <v>141.4555499119358</v>
+        <v>141.4555347881243</v>
       </c>
       <c r="F44" t="n">
-        <v>143.155393737904</v>
+        <v>143.1553784323526</v>
       </c>
       <c r="G44" t="n">
         <v>10527800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>141.0877380371094</v>
+        <v>141.0877227783203</v>
       </c>
       <c r="D45" t="n">
-        <v>141.7835961642497</v>
+        <v>141.7835808302028</v>
       </c>
       <c r="E45" t="n">
-        <v>140.1930849711274</v>
+        <v>140.193069809096</v>
       </c>
       <c r="F45" t="n">
-        <v>140.8491719759083</v>
+        <v>140.8491567429204</v>
       </c>
       <c r="G45" t="n">
         <v>7498700</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>141.1772155761719</v>
+        <v>141.1772003173828</v>
       </c>
       <c r="D52" t="n">
-        <v>141.882993732033</v>
+        <v>141.8829783969616</v>
       </c>
       <c r="E52" t="n">
-        <v>140.95851990776</v>
+        <v>140.9585046726081</v>
       </c>
       <c r="F52" t="n">
-        <v>141.4257320022546</v>
+        <v>141.4257167166052</v>
       </c>
       <c r="G52" t="n">
         <v>2818300</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>138.9902801513672</v>
+        <v>138.9902648925781</v>
       </c>
       <c r="D53" t="n">
-        <v>140.839227880941</v>
+        <v>140.8392124191687</v>
       </c>
       <c r="E53" t="n">
-        <v>138.9703945893022</v>
+        <v>138.9703793326962</v>
       </c>
       <c r="F53" t="n">
-        <v>140.461493211144</v>
+        <v>140.4614777908405</v>
       </c>
       <c r="G53" t="n">
         <v>3503300</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>138.7218627929688</v>
+        <v>138.7218780517578</v>
       </c>
       <c r="D54" t="n">
-        <v>139.3580641944511</v>
+        <v>139.3580795232195</v>
       </c>
       <c r="E54" t="n">
-        <v>137.0816453896048</v>
+        <v>137.0816604679772</v>
       </c>
       <c r="F54" t="n">
-        <v>137.4295744301408</v>
+        <v>137.4295895467839</v>
       </c>
       <c r="G54" t="n">
         <v>5703700</v>
@@ -3359,7 +3359,99 @@
         <v>157.2599945068359</v>
       </c>
       <c r="G127" t="n">
-        <v>2571661</v>
+        <v>2578500</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C128" t="n">
+        <v>156.3399963378906</v>
+      </c>
+      <c r="D128" t="n">
+        <v>157.4400024414062</v>
+      </c>
+      <c r="E128" t="n">
+        <v>155.9499969482422</v>
+      </c>
+      <c r="F128" t="n">
+        <v>157.2799987792969</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1929500</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C129" t="n">
+        <v>155.8099975585938</v>
+      </c>
+      <c r="D129" t="n">
+        <v>155.9199981689453</v>
+      </c>
+      <c r="E129" t="n">
+        <v>154.2599945068359</v>
+      </c>
+      <c r="F129" t="n">
+        <v>155.1499938964844</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1900400</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C130" t="n">
+        <v>157</v>
+      </c>
+      <c r="D130" t="n">
+        <v>157.2400054931641</v>
+      </c>
+      <c r="E130" t="n">
+        <v>156.0500030517578</v>
+      </c>
+      <c r="F130" t="n">
+        <v>156.3300018310547</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1660600</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C131" t="n">
+        <v>157.6300048828125</v>
+      </c>
+      <c r="D131" t="n">
+        <v>157.7299957275391</v>
+      </c>
+      <c r="E131" t="n">
+        <v>156.2899932861328</v>
+      </c>
+      <c r="F131" t="n">
+        <v>157.2100067138672</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1759600</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3451,7 +3451,122 @@
         <v>157.2100067138672</v>
       </c>
       <c r="G131" t="n">
-        <v>1759600</v>
+        <v>1760500</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C132" t="n">
+        <v>155.8099975585938</v>
+      </c>
+      <c r="D132" t="n">
+        <v>156.9400024414062</v>
+      </c>
+      <c r="E132" t="n">
+        <v>155.5700073242188</v>
+      </c>
+      <c r="F132" t="n">
+        <v>156.7100067138672</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2388400</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C133" t="n">
+        <v>156.7799987792969</v>
+      </c>
+      <c r="D133" t="n">
+        <v>157.2599945068359</v>
+      </c>
+      <c r="E133" t="n">
+        <v>156.3300018310547</v>
+      </c>
+      <c r="F133" t="n">
+        <v>156.6399993896484</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1744200</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C134" t="n">
+        <v>157.2899932861328</v>
+      </c>
+      <c r="D134" t="n">
+        <v>157.5099945068359</v>
+      </c>
+      <c r="E134" t="n">
+        <v>156.2100067138672</v>
+      </c>
+      <c r="F134" t="n">
+        <v>157.25</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1960600</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C135" t="n">
+        <v>156.1300048828125</v>
+      </c>
+      <c r="D135" t="n">
+        <v>156.9499969482422</v>
+      </c>
+      <c r="E135" t="n">
+        <v>155.6600036621094</v>
+      </c>
+      <c r="F135" t="n">
+        <v>156.4499969482422</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1890000</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C136" t="n">
+        <v>154.7799987792969</v>
+      </c>
+      <c r="D136" t="n">
+        <v>155.4299926757812</v>
+      </c>
+      <c r="E136" t="n">
+        <v>153.8500061035156</v>
+      </c>
+      <c r="F136" t="n">
+        <v>154.2400054931641</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2359400</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3566,7 +3566,191 @@
         <v>154.2400054931641</v>
       </c>
       <c r="G136" t="n">
-        <v>2359400</v>
+        <v>2361300</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C137" t="n">
+        <v>154.2899932861328</v>
+      </c>
+      <c r="D137" t="n">
+        <v>155.6900024414062</v>
+      </c>
+      <c r="E137" t="n">
+        <v>154.1799926757812</v>
+      </c>
+      <c r="F137" t="n">
+        <v>155.3899993896484</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2124200</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C138" t="n">
+        <v>156.1399993896484</v>
+      </c>
+      <c r="D138" t="n">
+        <v>156.3000030517578</v>
+      </c>
+      <c r="E138" t="n">
+        <v>155.1000061035156</v>
+      </c>
+      <c r="F138" t="n">
+        <v>155.5500030517578</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1458800</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C139" t="n">
+        <v>156.0200042724609</v>
+      </c>
+      <c r="D139" t="n">
+        <v>156.4900054931641</v>
+      </c>
+      <c r="E139" t="n">
+        <v>155.7799987792969</v>
+      </c>
+      <c r="F139" t="n">
+        <v>155.8600006103516</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1448600</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C140" t="n">
+        <v>154.3099975585938</v>
+      </c>
+      <c r="D140" t="n">
+        <v>155.1000061035156</v>
+      </c>
+      <c r="E140" t="n">
+        <v>153.5599975585938</v>
+      </c>
+      <c r="F140" t="n">
+        <v>154.2700042724609</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2084500</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C141" t="n">
+        <v>154.1999969482422</v>
+      </c>
+      <c r="D141" t="n">
+        <v>155.2899932861328</v>
+      </c>
+      <c r="E141" t="n">
+        <v>153.8800048828125</v>
+      </c>
+      <c r="F141" t="n">
+        <v>154.3999938964844</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2944200</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C142" t="n">
+        <v>154.4499969482422</v>
+      </c>
+      <c r="D142" t="n">
+        <v>155.7400054931641</v>
+      </c>
+      <c r="E142" t="n">
+        <v>153.6799926757812</v>
+      </c>
+      <c r="F142" t="n">
+        <v>155.4799957275391</v>
+      </c>
+      <c r="G142" t="n">
+        <v>4989400</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C143" t="n">
+        <v>154.3500061035156</v>
+      </c>
+      <c r="D143" t="n">
+        <v>154.8200073242188</v>
+      </c>
+      <c r="E143" t="n">
+        <v>153.2400054931641</v>
+      </c>
+      <c r="F143" t="n">
+        <v>153.8800048828125</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2579800</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C144" t="n">
+        <v>152.2200012207031</v>
+      </c>
+      <c r="D144" t="n">
+        <v>154.9799957275391</v>
+      </c>
+      <c r="E144" t="n">
+        <v>152.1300048828125</v>
+      </c>
+      <c r="F144" t="n">
+        <v>153.9799957275391</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4029310</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3750,7 +3750,145 @@
         <v>153.9799957275391</v>
       </c>
       <c r="G144" t="n">
-        <v>4029310</v>
+        <v>4036100</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C145" t="n">
+        <v>155.4499969482422</v>
+      </c>
+      <c r="D145" t="n">
+        <v>155.5700073242188</v>
+      </c>
+      <c r="E145" t="n">
+        <v>153.7700042724609</v>
+      </c>
+      <c r="F145" t="n">
+        <v>153.9799957275391</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2716700</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C146" t="n">
+        <v>155.8600006103516</v>
+      </c>
+      <c r="D146" t="n">
+        <v>156.25</v>
+      </c>
+      <c r="E146" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="F146" t="n">
+        <v>155.9799957275391</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3216800</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C147" t="n">
+        <v>157.6100006103516</v>
+      </c>
+      <c r="D147" t="n">
+        <v>157.7200012207031</v>
+      </c>
+      <c r="E147" t="n">
+        <v>156.1900024414062</v>
+      </c>
+      <c r="F147" t="n">
+        <v>156.3999938964844</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2439300</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C148" t="n">
+        <v>160.4499969482422</v>
+      </c>
+      <c r="D148" t="n">
+        <v>160.7799987792969</v>
+      </c>
+      <c r="E148" t="n">
+        <v>158.5099945068359</v>
+      </c>
+      <c r="F148" t="n">
+        <v>158.5899963378906</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2839000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C149" t="n">
+        <v>160.1699981689453</v>
+      </c>
+      <c r="D149" t="n">
+        <v>162</v>
+      </c>
+      <c r="E149" t="n">
+        <v>160.1199951171875</v>
+      </c>
+      <c r="F149" t="n">
+        <v>161.3399963378906</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2386000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C150" t="n">
+        <v>159.9199981689453</v>
+      </c>
+      <c r="D150" t="n">
+        <v>160.6799011230469</v>
+      </c>
+      <c r="E150" t="n">
+        <v>159.7649993896484</v>
+      </c>
+      <c r="F150" t="n">
+        <v>160.1000061035156</v>
+      </c>
+      <c r="G150" t="n">
+        <v>4265575</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>141.2567291259766</v>
+        <v>141.2567443847656</v>
       </c>
       <c r="D2" t="n">
-        <v>141.6245285475221</v>
+        <v>141.6245438460415</v>
       </c>
       <c r="E2" t="n">
-        <v>140.5410006739373</v>
+        <v>140.5410158554122</v>
       </c>
       <c r="F2" t="n">
-        <v>141.4157680955784</v>
+        <v>141.4157833715471</v>
       </c>
       <c r="G2" t="n">
         <v>4387700</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>143.2846221923828</v>
+        <v>143.2846374511719</v>
       </c>
       <c r="D4" t="n">
-        <v>143.3641492645759</v>
+        <v>143.364164531834</v>
       </c>
       <c r="E4" t="n">
-        <v>142.6384855871414</v>
+        <v>142.6385007771216</v>
       </c>
       <c r="F4" t="n">
-        <v>142.6981270992267</v>
+        <v>142.6981422955583</v>
       </c>
       <c r="G4" t="n">
         <v>4700600</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>145.9288330078125</v>
+        <v>145.9288482666016</v>
       </c>
       <c r="D19" t="n">
-        <v>146.386094689268</v>
+        <v>146.3861099958698</v>
       </c>
       <c r="E19" t="n">
-        <v>145.451685767265</v>
+        <v>145.451700976162</v>
       </c>
       <c r="F19" t="n">
-        <v>146.2767468666178</v>
+        <v>146.2767621617859</v>
       </c>
       <c r="G19" t="n">
         <v>4430300</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>144.7458953857422</v>
+        <v>144.7459106445312</v>
       </c>
       <c r="D23" t="n">
-        <v>145.6902546901213</v>
+        <v>145.6902700484627</v>
       </c>
       <c r="E23" t="n">
-        <v>143.5331341171332</v>
+        <v>143.5331492480756</v>
       </c>
       <c r="F23" t="n">
-        <v>145.5809068653045</v>
+        <v>145.5809222121186</v>
       </c>
       <c r="G23" t="n">
         <v>5718700</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>146.7936859130859</v>
+        <v>146.7936706542969</v>
       </c>
       <c r="D27" t="n">
-        <v>147.0521375447568</v>
+        <v>147.0521222591024</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4517062658755</v>
+        <v>145.4516911465814</v>
       </c>
       <c r="F27" t="n">
-        <v>145.6008100594857</v>
+        <v>145.6007949246927</v>
       </c>
       <c r="G27" t="n">
         <v>3890200</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>146.7042236328125</v>
+        <v>146.7042083740234</v>
       </c>
       <c r="D28" t="n">
-        <v>147.4199521786005</v>
+        <v>147.4199368453681</v>
       </c>
       <c r="E28" t="n">
-        <v>146.6644525090246</v>
+        <v>146.6644372543722</v>
       </c>
       <c r="F28" t="n">
-        <v>147.3404250992641</v>
+        <v>147.3404097743034</v>
       </c>
       <c r="G28" t="n">
         <v>3727000</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>146.823486328125</v>
+        <v>146.8235015869141</v>
       </c>
       <c r="D37" t="n">
-        <v>147.0024260239031</v>
+        <v>147.0024413012886</v>
       </c>
       <c r="E37" t="n">
-        <v>145.4715565031693</v>
+        <v>145.4715716214576</v>
       </c>
       <c r="F37" t="n">
-        <v>145.7300232672668</v>
+        <v>145.7300384124165</v>
       </c>
       <c r="G37" t="n">
         <v>6002800</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>146.0779418945312</v>
+        <v>146.0779571533203</v>
       </c>
       <c r="D41" t="n">
-        <v>146.5849250755847</v>
+        <v>146.5849403873314</v>
       </c>
       <c r="E41" t="n">
-        <v>144.437739665593</v>
+        <v>144.4377547530523</v>
       </c>
       <c r="F41" t="n">
-        <v>144.6067290031982</v>
+        <v>144.6067441083095</v>
       </c>
       <c r="G41" t="n">
         <v>7713300</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>144.3979797363281</v>
+        <v>144.3979644775391</v>
       </c>
       <c r="D43" t="n">
-        <v>144.7260232411855</v>
+        <v>144.7260079477315</v>
       </c>
       <c r="E43" t="n">
-        <v>143.0659353238083</v>
+        <v>143.0659202057788</v>
       </c>
       <c r="F43" t="n">
-        <v>143.6226096951158</v>
+        <v>143.6225945182615</v>
       </c>
       <c r="G43" t="n">
         <v>5318000</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>142.7180023193359</v>
+        <v>142.718017578125</v>
       </c>
       <c r="D44" t="n">
-        <v>144.0003402409777</v>
+        <v>144.0003556368688</v>
       </c>
       <c r="E44" t="n">
-        <v>141.4555347881243</v>
+        <v>141.4555499119358</v>
       </c>
       <c r="F44" t="n">
-        <v>143.1553784323526</v>
+        <v>143.155393737904</v>
       </c>
       <c r="G44" t="n">
         <v>10527800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>141.0877227783203</v>
+        <v>141.0877380371094</v>
       </c>
       <c r="D45" t="n">
-        <v>141.7835808302028</v>
+        <v>141.7835961642497</v>
       </c>
       <c r="E45" t="n">
-        <v>140.193069809096</v>
+        <v>140.1930849711274</v>
       </c>
       <c r="F45" t="n">
-        <v>140.8491567429204</v>
+        <v>140.8491719759083</v>
       </c>
       <c r="G45" t="n">
         <v>7498700</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>141.1772003173828</v>
+        <v>141.1772155761719</v>
       </c>
       <c r="D52" t="n">
-        <v>141.8829783969616</v>
+        <v>141.882993732033</v>
       </c>
       <c r="E52" t="n">
-        <v>140.9585046726081</v>
+        <v>140.95851990776</v>
       </c>
       <c r="F52" t="n">
-        <v>141.4257167166052</v>
+        <v>141.4257320022546</v>
       </c>
       <c r="G52" t="n">
         <v>2818300</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>138.9902648925781</v>
+        <v>138.9902801513672</v>
       </c>
       <c r="D53" t="n">
-        <v>140.8392124191687</v>
+        <v>140.839227880941</v>
       </c>
       <c r="E53" t="n">
-        <v>138.9703793326962</v>
+        <v>138.9703945893022</v>
       </c>
       <c r="F53" t="n">
-        <v>140.4614777908405</v>
+        <v>140.461493211144</v>
       </c>
       <c r="G53" t="n">
         <v>3503300</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>138.7218780517578</v>
+        <v>138.7218627929688</v>
       </c>
       <c r="D54" t="n">
-        <v>139.3580795232195</v>
+        <v>139.3580641944511</v>
       </c>
       <c r="E54" t="n">
-        <v>137.0816604679772</v>
+        <v>137.0816453896048</v>
       </c>
       <c r="F54" t="n">
-        <v>137.4295895467839</v>
+        <v>137.4295744301408</v>
       </c>
       <c r="G54" t="n">
         <v>5703700</v>
@@ -3879,16 +3879,154 @@
         <v>159.9199981689453</v>
       </c>
       <c r="D150" t="n">
-        <v>160.6799011230469</v>
+        <v>160.6799926757812</v>
       </c>
       <c r="E150" t="n">
-        <v>159.7649993896484</v>
+        <v>159.7700042724609</v>
       </c>
       <c r="F150" t="n">
         <v>160.1000061035156</v>
       </c>
       <c r="G150" t="n">
-        <v>4265575</v>
+        <v>4295900</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C151" t="n">
+        <v>161.3000030517578</v>
+      </c>
+      <c r="D151" t="n">
+        <v>161.3800048828125</v>
+      </c>
+      <c r="E151" t="n">
+        <v>160.5299987792969</v>
+      </c>
+      <c r="F151" t="n">
+        <v>161.0099945068359</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2952700</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C152" t="n">
+        <v>160.9700012207031</v>
+      </c>
+      <c r="D152" t="n">
+        <v>161.3500061035156</v>
+      </c>
+      <c r="E152" t="n">
+        <v>160.8500061035156</v>
+      </c>
+      <c r="F152" t="n">
+        <v>161</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2425900</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C153" t="n">
+        <v>160.8200073242188</v>
+      </c>
+      <c r="D153" t="n">
+        <v>161.5399932861328</v>
+      </c>
+      <c r="E153" t="n">
+        <v>160.5399932861328</v>
+      </c>
+      <c r="F153" t="n">
+        <v>161.4499969482422</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1646000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C154" t="n">
+        <v>161.5299987792969</v>
+      </c>
+      <c r="D154" t="n">
+        <v>162</v>
+      </c>
+      <c r="E154" t="n">
+        <v>161.3300018310547</v>
+      </c>
+      <c r="F154" t="n">
+        <v>161.8999938964844</v>
+      </c>
+      <c r="G154" t="n">
+        <v>3041600</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C155" t="n">
+        <v>162.3899993896484</v>
+      </c>
+      <c r="D155" t="n">
+        <v>162.6799926757812</v>
+      </c>
+      <c r="E155" t="n">
+        <v>161.8200073242188</v>
+      </c>
+      <c r="F155" t="n">
+        <v>161.9199981689453</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2324400</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C156" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="D156" t="n">
+        <v>162.7100067138672</v>
+      </c>
+      <c r="E156" t="n">
+        <v>162.0050048828125</v>
+      </c>
+      <c r="F156" t="n">
+        <v>162.5599975585938</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1911123</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4020,13 +4020,59 @@
         <v>162.7100067138672</v>
       </c>
       <c r="E156" t="n">
-        <v>162.0050048828125</v>
+        <v>162.0099945068359</v>
       </c>
       <c r="F156" t="n">
         <v>162.5599975585938</v>
       </c>
       <c r="G156" t="n">
-        <v>1911123</v>
+        <v>1925400</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C157" t="n">
+        <v>161.8300018310547</v>
+      </c>
+      <c r="D157" t="n">
+        <v>162.5599975585938</v>
+      </c>
+      <c r="E157" t="n">
+        <v>161.7700042724609</v>
+      </c>
+      <c r="F157" t="n">
+        <v>162.2700042724609</v>
+      </c>
+      <c r="G157" t="n">
+        <v>3566300</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C158" t="n">
+        <v>160.0599975585938</v>
+      </c>
+      <c r="D158" t="n">
+        <v>161.0299987792969</v>
+      </c>
+      <c r="E158" t="n">
+        <v>160</v>
+      </c>
+      <c r="F158" t="n">
+        <v>160.8099975585938</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1937327</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>141.2567443847656</v>
+        <v>141.2567291259766</v>
       </c>
       <c r="D2" t="n">
-        <v>141.6245438460415</v>
+        <v>141.6245285475221</v>
       </c>
       <c r="E2" t="n">
-        <v>140.5410158554122</v>
+        <v>140.5410006739373</v>
       </c>
       <c r="F2" t="n">
-        <v>141.4157833715471</v>
+        <v>141.4157680955784</v>
       </c>
       <c r="G2" t="n">
         <v>4387700</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>143.2846374511719</v>
+        <v>143.2846221923828</v>
       </c>
       <c r="D4" t="n">
-        <v>143.364164531834</v>
+        <v>143.3641492645759</v>
       </c>
       <c r="E4" t="n">
-        <v>142.6385007771216</v>
+        <v>142.6384855871414</v>
       </c>
       <c r="F4" t="n">
-        <v>142.6981422955583</v>
+        <v>142.6981270992267</v>
       </c>
       <c r="G4" t="n">
         <v>4700600</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>145.9288482666016</v>
+        <v>145.9288330078125</v>
       </c>
       <c r="D19" t="n">
-        <v>146.3861099958698</v>
+        <v>146.386094689268</v>
       </c>
       <c r="E19" t="n">
-        <v>145.451700976162</v>
+        <v>145.451685767265</v>
       </c>
       <c r="F19" t="n">
-        <v>146.2767621617859</v>
+        <v>146.2767468666178</v>
       </c>
       <c r="G19" t="n">
         <v>4430300</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>144.7459106445312</v>
+        <v>144.7458953857422</v>
       </c>
       <c r="D23" t="n">
-        <v>145.6902700484627</v>
+        <v>145.6902546901213</v>
       </c>
       <c r="E23" t="n">
-        <v>143.5331492480756</v>
+        <v>143.5331341171332</v>
       </c>
       <c r="F23" t="n">
-        <v>145.5809222121186</v>
+        <v>145.5809068653045</v>
       </c>
       <c r="G23" t="n">
         <v>5718700</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>146.7936706542969</v>
+        <v>146.7936859130859</v>
       </c>
       <c r="D27" t="n">
-        <v>147.0521222591024</v>
+        <v>147.0521375447568</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4516911465814</v>
+        <v>145.4517062658755</v>
       </c>
       <c r="F27" t="n">
-        <v>145.6007949246927</v>
+        <v>145.6008100594857</v>
       </c>
       <c r="G27" t="n">
         <v>3890200</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>146.7042083740234</v>
+        <v>146.7042236328125</v>
       </c>
       <c r="D28" t="n">
-        <v>147.4199368453681</v>
+        <v>147.4199521786005</v>
       </c>
       <c r="E28" t="n">
-        <v>146.6644372543722</v>
+        <v>146.6644525090246</v>
       </c>
       <c r="F28" t="n">
-        <v>147.3404097743034</v>
+        <v>147.3404250992641</v>
       </c>
       <c r="G28" t="n">
         <v>3727000</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>146.8235015869141</v>
+        <v>146.823486328125</v>
       </c>
       <c r="D37" t="n">
-        <v>147.0024413012886</v>
+        <v>147.0024260239031</v>
       </c>
       <c r="E37" t="n">
-        <v>145.4715716214576</v>
+        <v>145.4715565031693</v>
       </c>
       <c r="F37" t="n">
-        <v>145.7300384124165</v>
+        <v>145.7300232672668</v>
       </c>
       <c r="G37" t="n">
         <v>6002800</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>146.0779571533203</v>
+        <v>146.0779418945312</v>
       </c>
       <c r="D41" t="n">
-        <v>146.5849403873314</v>
+        <v>146.5849250755847</v>
       </c>
       <c r="E41" t="n">
-        <v>144.4377547530523</v>
+        <v>144.437739665593</v>
       </c>
       <c r="F41" t="n">
-        <v>144.6067441083095</v>
+        <v>144.6067290031982</v>
       </c>
       <c r="G41" t="n">
         <v>7713300</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>144.3979644775391</v>
+        <v>144.3979797363281</v>
       </c>
       <c r="D43" t="n">
-        <v>144.7260079477315</v>
+        <v>144.7260232411855</v>
       </c>
       <c r="E43" t="n">
-        <v>143.0659202057788</v>
+        <v>143.0659353238083</v>
       </c>
       <c r="F43" t="n">
-        <v>143.6225945182615</v>
+        <v>143.6226096951158</v>
       </c>
       <c r="G43" t="n">
         <v>5318000</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>142.718017578125</v>
+        <v>142.7180023193359</v>
       </c>
       <c r="D44" t="n">
-        <v>144.0003556368688</v>
+        <v>144.0003402409777</v>
       </c>
       <c r="E44" t="n">
-        <v>141.4555499119358</v>
+        <v>141.4555347881243</v>
       </c>
       <c r="F44" t="n">
-        <v>143.155393737904</v>
+        <v>143.1553784323526</v>
       </c>
       <c r="G44" t="n">
         <v>10527800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>141.0877380371094</v>
+        <v>141.0877227783203</v>
       </c>
       <c r="D45" t="n">
-        <v>141.7835961642497</v>
+        <v>141.7835808302028</v>
       </c>
       <c r="E45" t="n">
-        <v>140.1930849711274</v>
+        <v>140.193069809096</v>
       </c>
       <c r="F45" t="n">
-        <v>140.8491719759083</v>
+        <v>140.8491567429204</v>
       </c>
       <c r="G45" t="n">
         <v>7498700</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>141.1772155761719</v>
+        <v>141.1772003173828</v>
       </c>
       <c r="D52" t="n">
-        <v>141.882993732033</v>
+        <v>141.8829783969616</v>
       </c>
       <c r="E52" t="n">
-        <v>140.95851990776</v>
+        <v>140.9585046726081</v>
       </c>
       <c r="F52" t="n">
-        <v>141.4257320022546</v>
+        <v>141.4257167166052</v>
       </c>
       <c r="G52" t="n">
         <v>2818300</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>138.9902801513672</v>
+        <v>138.9902648925781</v>
       </c>
       <c r="D53" t="n">
-        <v>140.839227880941</v>
+        <v>140.8392124191687</v>
       </c>
       <c r="E53" t="n">
-        <v>138.9703945893022</v>
+        <v>138.9703793326962</v>
       </c>
       <c r="F53" t="n">
-        <v>140.461493211144</v>
+        <v>140.4614777908405</v>
       </c>
       <c r="G53" t="n">
         <v>3503300</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>138.7218627929688</v>
+        <v>138.7218780517578</v>
       </c>
       <c r="D54" t="n">
-        <v>139.3580641944511</v>
+        <v>139.3580795232195</v>
       </c>
       <c r="E54" t="n">
-        <v>137.0816453896048</v>
+        <v>137.0816604679772</v>
       </c>
       <c r="F54" t="n">
-        <v>137.4295744301408</v>
+        <v>137.4295895467839</v>
       </c>
       <c r="G54" t="n">
         <v>5703700</v>
@@ -4072,7 +4072,30 @@
         <v>160.8099975585938</v>
       </c>
       <c r="G158" t="n">
-        <v>1937327</v>
+        <v>1975500</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C159" t="n">
+        <v>160.7149963378906</v>
+      </c>
+      <c r="D159" t="n">
+        <v>161.2100067138672</v>
+      </c>
+      <c r="E159" t="n">
+        <v>160.5350036621094</v>
+      </c>
+      <c r="F159" t="n">
+        <v>161.0099945068359</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2145687</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>141.2567291259766</v>
+        <v>141.2567443847656</v>
       </c>
       <c r="D2" t="n">
-        <v>141.6245285475221</v>
+        <v>141.6245438460415</v>
       </c>
       <c r="E2" t="n">
-        <v>140.5410006739373</v>
+        <v>140.5410158554122</v>
       </c>
       <c r="F2" t="n">
-        <v>141.4157680955784</v>
+        <v>141.4157833715471</v>
       </c>
       <c r="G2" t="n">
         <v>4387700</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>143.2846221923828</v>
+        <v>143.2846374511719</v>
       </c>
       <c r="D4" t="n">
-        <v>143.3641492645759</v>
+        <v>143.364164531834</v>
       </c>
       <c r="E4" t="n">
-        <v>142.6384855871414</v>
+        <v>142.6385007771216</v>
       </c>
       <c r="F4" t="n">
-        <v>142.6981270992267</v>
+        <v>142.6981422955583</v>
       </c>
       <c r="G4" t="n">
         <v>4700600</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>145.9288330078125</v>
+        <v>145.9288482666016</v>
       </c>
       <c r="D19" t="n">
-        <v>146.386094689268</v>
+        <v>146.3861099958698</v>
       </c>
       <c r="E19" t="n">
-        <v>145.451685767265</v>
+        <v>145.451700976162</v>
       </c>
       <c r="F19" t="n">
-        <v>146.2767468666178</v>
+        <v>146.2767621617859</v>
       </c>
       <c r="G19" t="n">
         <v>4430300</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>144.7458953857422</v>
+        <v>144.7459106445312</v>
       </c>
       <c r="D23" t="n">
-        <v>145.6902546901213</v>
+        <v>145.6902700484627</v>
       </c>
       <c r="E23" t="n">
-        <v>143.5331341171332</v>
+        <v>143.5331492480756</v>
       </c>
       <c r="F23" t="n">
-        <v>145.5809068653045</v>
+        <v>145.5809222121186</v>
       </c>
       <c r="G23" t="n">
         <v>5718700</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>146.7936859130859</v>
+        <v>146.7936706542969</v>
       </c>
       <c r="D27" t="n">
-        <v>147.0521375447568</v>
+        <v>147.0521222591024</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4517062658755</v>
+        <v>145.4516911465814</v>
       </c>
       <c r="F27" t="n">
-        <v>145.6008100594857</v>
+        <v>145.6007949246927</v>
       </c>
       <c r="G27" t="n">
         <v>3890200</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>146.7042236328125</v>
+        <v>146.7042083740234</v>
       </c>
       <c r="D28" t="n">
-        <v>147.4199521786005</v>
+        <v>147.4199368453681</v>
       </c>
       <c r="E28" t="n">
-        <v>146.6644525090246</v>
+        <v>146.6644372543722</v>
       </c>
       <c r="F28" t="n">
-        <v>147.3404250992641</v>
+        <v>147.3404097743034</v>
       </c>
       <c r="G28" t="n">
         <v>3727000</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>146.823486328125</v>
+        <v>146.8235015869141</v>
       </c>
       <c r="D37" t="n">
-        <v>147.0024260239031</v>
+        <v>147.0024413012886</v>
       </c>
       <c r="E37" t="n">
-        <v>145.4715565031693</v>
+        <v>145.4715716214576</v>
       </c>
       <c r="F37" t="n">
-        <v>145.7300232672668</v>
+        <v>145.7300384124165</v>
       </c>
       <c r="G37" t="n">
         <v>6002800</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>146.0779418945312</v>
+        <v>146.0779571533203</v>
       </c>
       <c r="D41" t="n">
-        <v>146.5849250755847</v>
+        <v>146.5849403873314</v>
       </c>
       <c r="E41" t="n">
-        <v>144.437739665593</v>
+        <v>144.4377547530523</v>
       </c>
       <c r="F41" t="n">
-        <v>144.6067290031982</v>
+        <v>144.6067441083095</v>
       </c>
       <c r="G41" t="n">
         <v>7713300</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>144.3979797363281</v>
+        <v>144.3979644775391</v>
       </c>
       <c r="D43" t="n">
-        <v>144.7260232411855</v>
+        <v>144.7260079477315</v>
       </c>
       <c r="E43" t="n">
-        <v>143.0659353238083</v>
+        <v>143.0659202057788</v>
       </c>
       <c r="F43" t="n">
-        <v>143.6226096951158</v>
+        <v>143.6225945182615</v>
       </c>
       <c r="G43" t="n">
         <v>5318000</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>142.7180023193359</v>
+        <v>142.718017578125</v>
       </c>
       <c r="D44" t="n">
-        <v>144.0003402409777</v>
+        <v>144.0003556368688</v>
       </c>
       <c r="E44" t="n">
-        <v>141.4555347881243</v>
+        <v>141.4555499119358</v>
       </c>
       <c r="F44" t="n">
-        <v>143.1553784323526</v>
+        <v>143.155393737904</v>
       </c>
       <c r="G44" t="n">
         <v>10527800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>141.0877227783203</v>
+        <v>141.0877380371094</v>
       </c>
       <c r="D45" t="n">
-        <v>141.7835808302028</v>
+        <v>141.7835961642497</v>
       </c>
       <c r="E45" t="n">
-        <v>140.193069809096</v>
+        <v>140.1930849711274</v>
       </c>
       <c r="F45" t="n">
-        <v>140.8491567429204</v>
+        <v>140.8491719759083</v>
       </c>
       <c r="G45" t="n">
         <v>7498700</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>141.1772003173828</v>
+        <v>141.1772155761719</v>
       </c>
       <c r="D52" t="n">
-        <v>141.8829783969616</v>
+        <v>141.882993732033</v>
       </c>
       <c r="E52" t="n">
-        <v>140.9585046726081</v>
+        <v>140.95851990776</v>
       </c>
       <c r="F52" t="n">
-        <v>141.4257167166052</v>
+        <v>141.4257320022546</v>
       </c>
       <c r="G52" t="n">
         <v>2818300</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>138.9902648925781</v>
+        <v>138.9902801513672</v>
       </c>
       <c r="D53" t="n">
-        <v>140.8392124191687</v>
+        <v>140.839227880941</v>
       </c>
       <c r="E53" t="n">
-        <v>138.9703793326962</v>
+        <v>138.9703945893022</v>
       </c>
       <c r="F53" t="n">
-        <v>140.4614777908405</v>
+        <v>140.461493211144</v>
       </c>
       <c r="G53" t="n">
         <v>3503300</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>138.7218780517578</v>
+        <v>138.7218627929688</v>
       </c>
       <c r="D54" t="n">
-        <v>139.3580795232195</v>
+        <v>139.3580641944511</v>
       </c>
       <c r="E54" t="n">
-        <v>137.0816604679772</v>
+        <v>137.0816453896048</v>
       </c>
       <c r="F54" t="n">
-        <v>137.4295895467839</v>
+        <v>137.4295744301408</v>
       </c>
       <c r="G54" t="n">
         <v>5703700</v>
@@ -4083,19 +4083,157 @@
         <v>46253</v>
       </c>
       <c r="C159" t="n">
-        <v>160.7149963378906</v>
+        <v>160.6999969482422</v>
       </c>
       <c r="D159" t="n">
-        <v>161.2100067138672</v>
+        <v>161.3699951171875</v>
       </c>
       <c r="E159" t="n">
-        <v>160.5350036621094</v>
+        <v>160.5399932861328</v>
       </c>
       <c r="F159" t="n">
         <v>161.0099945068359</v>
       </c>
       <c r="G159" t="n">
-        <v>2145687</v>
+        <v>2481500</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C160" t="n">
+        <v>159.9299926757812</v>
+      </c>
+      <c r="D160" t="n">
+        <v>160.8300018310547</v>
+      </c>
+      <c r="E160" t="n">
+        <v>159.8099975585938</v>
+      </c>
+      <c r="F160" t="n">
+        <v>160.3300018310547</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2072600</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C161" t="n">
+        <v>160.7700042724609</v>
+      </c>
+      <c r="D161" t="n">
+        <v>161.1699981689453</v>
+      </c>
+      <c r="E161" t="n">
+        <v>160.4600067138672</v>
+      </c>
+      <c r="F161" t="n">
+        <v>160.8999938964844</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1548400</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C162" t="n">
+        <v>160.1000061035156</v>
+      </c>
+      <c r="D162" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="E162" t="n">
+        <v>159.7799987792969</v>
+      </c>
+      <c r="F162" t="n">
+        <v>160.4799957275391</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1824900</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C163" t="n">
+        <v>160.9900054931641</v>
+      </c>
+      <c r="D163" t="n">
+        <v>161.0500030517578</v>
+      </c>
+      <c r="E163" t="n">
+        <v>160.3200073242188</v>
+      </c>
+      <c r="F163" t="n">
+        <v>160.8800048828125</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2568700</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C164" t="n">
+        <v>160.8699951171875</v>
+      </c>
+      <c r="D164" t="n">
+        <v>161.2899932861328</v>
+      </c>
+      <c r="E164" t="n">
+        <v>160.5800018310547</v>
+      </c>
+      <c r="F164" t="n">
+        <v>160.9299926757812</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1373000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="C165" t="n">
+        <v>161.5700073242188</v>
+      </c>
+      <c r="D165" t="n">
+        <v>161.7599945068359</v>
+      </c>
+      <c r="E165" t="n">
+        <v>160.9199981689453</v>
+      </c>
+      <c r="F165" t="n">
+        <v>161.1600036621094</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2013643</v>
       </c>
     </row>
   </sheetData>

--- a/Data/vt.xlsx
+++ b/Data/vt.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>46024</v>
       </c>
       <c r="C2" t="n">
-        <v>141.2567443847656</v>
+        <v>141.2567291259766</v>
       </c>
       <c r="D2" t="n">
-        <v>141.6245438460415</v>
+        <v>141.6245285475221</v>
       </c>
       <c r="E2" t="n">
-        <v>140.5410158554122</v>
+        <v>140.5410006739373</v>
       </c>
       <c r="F2" t="n">
-        <v>141.4157833715471</v>
+        <v>141.4157680955784</v>
       </c>
       <c r="G2" t="n">
         <v>4387700</v>
@@ -518,16 +518,16 @@
         <v>46028</v>
       </c>
       <c r="C4" t="n">
-        <v>143.2846374511719</v>
+        <v>143.2846221923828</v>
       </c>
       <c r="D4" t="n">
-        <v>143.364164531834</v>
+        <v>143.3641492645759</v>
       </c>
       <c r="E4" t="n">
-        <v>142.6385007771216</v>
+        <v>142.6384855871414</v>
       </c>
       <c r="F4" t="n">
-        <v>142.6981422955583</v>
+        <v>142.6981270992267</v>
       </c>
       <c r="G4" t="n">
         <v>4700600</v>
@@ -863,16 +863,16 @@
         <v>46050</v>
       </c>
       <c r="C19" t="n">
-        <v>145.9288482666016</v>
+        <v>145.9288330078125</v>
       </c>
       <c r="D19" t="n">
-        <v>146.3861099958698</v>
+        <v>146.386094689268</v>
       </c>
       <c r="E19" t="n">
-        <v>145.451700976162</v>
+        <v>145.451685767265</v>
       </c>
       <c r="F19" t="n">
-        <v>146.2767621617859</v>
+        <v>146.2767468666178</v>
       </c>
       <c r="G19" t="n">
         <v>4430300</v>
@@ -955,16 +955,16 @@
         <v>46056</v>
       </c>
       <c r="C23" t="n">
-        <v>144.7459106445312</v>
+        <v>144.7458953857422</v>
       </c>
       <c r="D23" t="n">
-        <v>145.6902700484627</v>
+        <v>145.6902546901213</v>
       </c>
       <c r="E23" t="n">
-        <v>143.5331492480756</v>
+        <v>143.5331341171332</v>
       </c>
       <c r="F23" t="n">
-        <v>145.5809222121186</v>
+        <v>145.5809068653045</v>
       </c>
       <c r="G23" t="n">
         <v>5718700</v>
@@ -1047,16 +1047,16 @@
         <v>46062</v>
       </c>
       <c r="C27" t="n">
-        <v>146.7936706542969</v>
+        <v>146.7936859130859</v>
       </c>
       <c r="D27" t="n">
-        <v>147.0521222591024</v>
+        <v>147.0521375447568</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4516911465814</v>
+        <v>145.4517062658755</v>
       </c>
       <c r="F27" t="n">
-        <v>145.6007949246927</v>
+        <v>145.6008100594857</v>
       </c>
       <c r="G27" t="n">
         <v>3890200</v>
@@ -1070,16 +1070,16 @@
         <v>46063</v>
       </c>
       <c r="C28" t="n">
-        <v>146.7042083740234</v>
+        <v>146.7042236328125</v>
       </c>
       <c r="D28" t="n">
-        <v>147.4199368453681</v>
+        <v>147.4199521786005</v>
       </c>
       <c r="E28" t="n">
-        <v>146.6644372543722</v>
+        <v>146.6644525090246</v>
       </c>
       <c r="F28" t="n">
-        <v>147.3404097743034</v>
+        <v>147.3404250992641</v>
       </c>
       <c r="G28" t="n">
         <v>3727000</v>
@@ -1277,16 +1277,16 @@
         <v>46077</v>
       </c>
       <c r="C37" t="n">
-        <v>146.8235015869141</v>
+        <v>146.823486328125</v>
       </c>
       <c r="D37" t="n">
-        <v>147.0024413012886</v>
+        <v>147.0024260239031</v>
       </c>
       <c r="E37" t="n">
-        <v>145.4715716214576</v>
+        <v>145.4715565031693</v>
       </c>
       <c r="F37" t="n">
-        <v>145.7300384124165</v>
+        <v>145.7300232672668</v>
       </c>
       <c r="G37" t="n">
         <v>6002800</v>
@@ -1369,16 +1369,16 @@
         <v>46083</v>
       </c>
       <c r="C41" t="n">
-        <v>146.0779571533203</v>
+        <v>146.0779418945312</v>
       </c>
       <c r="D41" t="n">
-        <v>146.5849403873314</v>
+        <v>146.5849250755847</v>
       </c>
       <c r="E41" t="n">
-        <v>144.4377547530523</v>
+        <v>144.437739665593</v>
       </c>
       <c r="F41" t="n">
-        <v>144.6067441083095</v>
+        <v>144.6067290031982</v>
       </c>
       <c r="G41" t="n">
         <v>7713300</v>
@@ -1415,16 +1415,16 @@
         <v>46085</v>
       </c>
       <c r="C43" t="n">
-        <v>144.3979644775391</v>
+        <v>144.3979797363281</v>
       </c>
       <c r="D43" t="n">
-        <v>144.7260079477315</v>
+        <v>144.7260232411855</v>
       </c>
       <c r="E43" t="n">
-        <v>143.0659202057788</v>
+        <v>143.0659353238083</v>
       </c>
       <c r="F43" t="n">
-        <v>143.6225945182615</v>
+        <v>143.6226096951158</v>
       </c>
       <c r="G43" t="n">
         <v>5318000</v>
@@ -1438,16 +1438,16 @@
         <v>46086</v>
       </c>
       <c r="C44" t="n">
-        <v>142.718017578125</v>
+        <v>142.7180023193359</v>
       </c>
       <c r="D44" t="n">
-        <v>144.0003556368688</v>
+        <v>144.0003402409777</v>
       </c>
       <c r="E44" t="n">
-        <v>141.4555499119358</v>
+        <v>141.4555347881243</v>
       </c>
       <c r="F44" t="n">
-        <v>143.155393737904</v>
+        <v>143.1553784323526</v>
       </c>
       <c r="G44" t="n">
         <v>10527800</v>
@@ -1461,16 +1461,16 @@
         <v>46087</v>
       </c>
       <c r="C45" t="n">
-        <v>141.0877380371094</v>
+        <v>141.0877227783203</v>
       </c>
       <c r="D45" t="n">
-        <v>141.7835961642497</v>
+        <v>141.7835808302028</v>
       </c>
       <c r="E45" t="n">
-        <v>140.1930849711274</v>
+        <v>140.193069809096</v>
       </c>
       <c r="F45" t="n">
-        <v>140.8491719759083</v>
+        <v>140.8491567429204</v>
       </c>
       <c r="G45" t="n">
         <v>7498700</v>
@@ -1622,16 +1622,16 @@
         <v>46098</v>
       </c>
       <c r="C52" t="n">
-        <v>141.1772155761719</v>
+        <v>141.1772003173828</v>
       </c>
       <c r="D52" t="n">
-        <v>141.882993732033</v>
+        <v>141.8829783969616</v>
       </c>
       <c r="E52" t="n">
-        <v>140.95851990776</v>
+        <v>140.9585046726081</v>
       </c>
       <c r="F52" t="n">
-        <v>141.4257320022546</v>
+        <v>141.4257167166052</v>
       </c>
       <c r="G52" t="n">
         <v>2818300</v>
@@ -1645,16 +1645,16 @@
         <v>46099</v>
       </c>
       <c r="C53" t="n">
-        <v>138.9902801513672</v>
+        <v>138.9902648925781</v>
       </c>
       <c r="D53" t="n">
-        <v>140.839227880941</v>
+        <v>140.8392124191687</v>
       </c>
       <c r="E53" t="n">
-        <v>138.9703945893022</v>
+        <v>138.9703793326962</v>
       </c>
       <c r="F53" t="n">
-        <v>140.461493211144</v>
+        <v>140.4614777908405</v>
       </c>
       <c r="G53" t="n">
         <v>3503300</v>
@@ -1668,16 +1668,16 @@
         <v>46100</v>
       </c>
       <c r="C54" t="n">
-        <v>138.7218627929688</v>
+        <v>138.7218780517578</v>
       </c>
       <c r="D54" t="n">
-        <v>139.3580641944511</v>
+        <v>139.3580795232195</v>
       </c>
       <c r="E54" t="n">
-        <v>137.0816453896048</v>
+        <v>137.0816604679772</v>
       </c>
       <c r="F54" t="n">
-        <v>137.4295744301408</v>
+        <v>137.4295895467839</v>
       </c>
       <c r="G54" t="n">
         <v>5703700</v>
@@ -4233,7 +4233,76 @@
         <v>161.1600036621094</v>
       </c>
       <c r="G165" t="n">
-        <v>2013643</v>
+        <v>2014900</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C166" t="n">
+        <v>161.0099945068359</v>
+      </c>
+      <c r="D166" t="n">
+        <v>162.1999969482422</v>
+      </c>
+      <c r="E166" t="n">
+        <v>160.7599945068359</v>
+      </c>
+      <c r="F166" t="n">
+        <v>161.7700042724609</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1592800</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C167" t="n">
+        <v>160.5500030517578</v>
+      </c>
+      <c r="D167" t="n">
+        <v>161</v>
+      </c>
+      <c r="E167" t="n">
+        <v>160.1699981689453</v>
+      </c>
+      <c r="F167" t="n">
+        <v>160.9700012207031</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2024700</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C168" t="n">
+        <v>159.3099975585938</v>
+      </c>
+      <c r="D168" t="n">
+        <v>160.1504974365234</v>
+      </c>
+      <c r="E168" t="n">
+        <v>158.9100036621094</v>
+      </c>
+      <c r="F168" t="n">
+        <v>159.6000061035156</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1943696</v>
       </c>
     </row>
   </sheetData>
